--- a/avance.xlsx
+++ b/avance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7866654A-F71E-41D2-B8F4-9C0852D358E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7D6A37-844D-4DCF-8FAE-4BAE589140EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Avance cosecha" sheetId="1" r:id="rId1"/>
@@ -509,7 +509,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -574,6 +574,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD8E4BC"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -665,7 +671,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -885,11 +891,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3230,22 +3247,22 @@
         <v>2000</v>
       </c>
       <c r="K44" s="1">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="L44" s="1">
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="M44" s="9">
         <f t="shared" si="0"/>
-        <v>0.43847993622110015</v>
+        <v>0.6909380813180972</v>
       </c>
       <c r="N44" s="10">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O44" s="11">
         <f t="shared" si="2"/>
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3366,11 +3383,11 @@
       </c>
       <c r="C50" s="20">
         <f>SUMIF(F$2:F$45,"Sj2",K$2:K$45)</f>
-        <v>1133.7399999999998</v>
+        <v>1171.7399999999998</v>
       </c>
       <c r="D50" s="21">
         <f>IF(B50&gt;0,C50/B50,"")</f>
-        <v>0.27814809998945045</v>
+        <v>0.28747089692666633</v>
       </c>
       <c r="E50" s="22">
         <f>IF(SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMIF(F$2:F$45,"Sj2",C$2:C$45),"")</f>
@@ -3378,15 +3395,15 @@
       </c>
       <c r="F50" s="22">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1556.9624693492337</v>
+        <v>1563.3080973594826</v>
       </c>
       <c r="G50" s="23">
         <f>IF(F50&lt;&gt;"",F50-E50,"")</f>
-        <v>-380.93641755787917</v>
+        <v>-374.59078954763027</v>
       </c>
       <c r="H50" s="24">
         <f>IF(AND(F50&lt;&gt;"",E50&gt;0),(F50-E50)/E50,"")</f>
-        <v>-0.19657187489583308</v>
+        <v>-0.19329738619411524</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3399,11 +3416,11 @@
       </c>
       <c r="C51" s="26">
         <f>SUM(C49:C50)</f>
-        <v>1584.11</v>
+        <v>1622.11</v>
       </c>
       <c r="D51" s="27">
         <f>IF(B51&gt;0,C51/B51,"")</f>
-        <v>0.3485620613021761</v>
+        <v>0.35692344929258246</v>
       </c>
       <c r="E51" s="28">
         <f>IF(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)),"")</f>
@@ -3411,15 +3428,15 @@
       </c>
       <c r="F51" s="28">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1587.2620840724439</v>
+        <v>1591.1360758518222</v>
       </c>
       <c r="G51" s="29">
         <f>IF(F51&lt;&gt;"",F51-E51,"")</f>
-        <v>-361.9255410733299</v>
+        <v>-358.05154929395167</v>
       </c>
       <c r="H51" s="30">
         <f>IF(AND(F51&lt;&gt;"",E51&gt;0),(F51-E51)/E51,"")</f>
-        <v>-0.18568019640811262</v>
+        <v>-0.18369270596368273</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3757,11 +3774,11 @@
       </c>
       <c r="D63" s="42">
         <f>SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="E63" s="43">
         <f t="shared" si="3"/>
-        <v>0.11155309110894655</v>
+        <v>0.13223122507060495</v>
       </c>
       <c r="F63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3769,15 +3786,15 @@
       </c>
       <c r="G63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1960.9756097560976</v>
+        <v>1928.3950617283951</v>
       </c>
       <c r="H63" s="45">
         <f t="shared" si="4"/>
-        <v>-97.479298307830504</v>
+        <v>-130.05984633553294</v>
       </c>
       <c r="I63" s="46">
         <f t="shared" si="5"/>
-        <v>-4.7355566510569956E-2</v>
+        <v>-6.3183237983998511E-2</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3791,11 +3808,11 @@
       </c>
       <c r="D64" s="55">
         <f>SUM(D55:D63)</f>
-        <v>1584.1100000000001</v>
+        <v>1622.1100000000001</v>
       </c>
       <c r="E64" s="56">
         <f t="shared" si="3"/>
-        <v>0.34856206130217621</v>
+        <v>0.35692344929258263</v>
       </c>
       <c r="F64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45),"")</f>
@@ -3803,15 +3820,15 @@
       </c>
       <c r="G64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1587.2620840724439</v>
+        <v>1591.1360758518222</v>
       </c>
       <c r="H64" s="58">
         <f t="shared" si="4"/>
-        <v>-361.92554107333035</v>
+        <v>-358.05154929395212</v>
       </c>
       <c r="I64" s="59">
         <f t="shared" si="5"/>
-        <v>-0.18568019640811281</v>
+        <v>-0.18369270596368292</v>
       </c>
     </row>
   </sheetData>
@@ -5564,21 +5581,21 @@
       </c>
     </row>
     <row r="69" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="31" t="s">
+      <c r="A69" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="B69" s="32" t="s">
+      <c r="B69" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="C69" s="15">
+      <c r="C69" s="78">
         <f>SUMPRODUCT((A$2:A$55="San Luis")*(D$2:D$55="Cz")*C$2:C$55)</f>
         <v>138.88</v>
       </c>
-      <c r="D69" s="15">
+      <c r="D69" s="78">
         <f>SUMPRODUCT((A$2:A$55="San Luis")*(D$2:D$55="Cz")*E$2:E$55)</f>
         <v>138.88</v>
       </c>
-      <c r="E69" s="16">
+      <c r="E69" s="79">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -5991,12 +6008,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="80" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="75"/>
+      <c r="E1" s="80"/>
       <c r="F1" t="s">
         <v>112</v>
       </c>
@@ -6126,11 +6141,11 @@
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E9" s="77">
+      <c r="E9" s="75">
         <f>+C8/E8</f>
         <v>76.229841441929807</v>
       </c>
-      <c r="F9" s="77">
+      <c r="F9" s="75">
         <f>+C8/F8</f>
         <v>1022.7272727272727</v>
       </c>

--- a/avance.xlsx
+++ b/avance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7D6A37-844D-4DCF-8FAE-4BAE589140EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6BCE2DB-7277-475D-BCE7-ACA0B9FBEC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1420,7 +1420,7 @@
         <v>28.41</v>
       </c>
       <c r="L5" s="1">
-        <v>1330</v>
+        <v>1339</v>
       </c>
       <c r="M5" s="9">
         <f t="shared" si="0"/>
@@ -1428,11 +1428,11 @@
       </c>
       <c r="N5" s="10">
         <f t="shared" si="1"/>
-        <v>-470</v>
+        <v>-461</v>
       </c>
       <c r="O5" s="11">
         <f t="shared" si="2"/>
-        <v>-0.26111111111111113</v>
+        <v>-0.25611111111111112</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -1520,7 +1520,7 @@
         <v>62.73</v>
       </c>
       <c r="L7" s="1">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="M7" s="9">
         <f t="shared" si="0"/>
@@ -1528,11 +1528,11 @@
       </c>
       <c r="N7" s="10">
         <f t="shared" si="1"/>
-        <v>-230</v>
+        <v>-237</v>
       </c>
       <c r="O7" s="11">
         <f t="shared" si="2"/>
-        <v>-0.12777777777777777</v>
+        <v>-0.13166666666666665</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -1566,17 +1566,23 @@
       <c r="J8" s="1">
         <v>1800</v>
       </c>
+      <c r="K8" s="1">
+        <v>29.7</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1723</v>
+      </c>
       <c r="M8" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N8" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O8" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="N8" s="10">
+        <f t="shared" si="1"/>
+        <v>-77</v>
+      </c>
+      <c r="O8" s="11">
+        <f t="shared" si="2"/>
+        <v>-4.2777777777777776E-2</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -1611,22 +1617,22 @@
         <v>1800</v>
       </c>
       <c r="K9" s="1">
-        <v>218</v>
+        <v>270.44</v>
       </c>
       <c r="L9" s="1">
-        <v>1280</v>
+        <v>1298</v>
       </c>
       <c r="M9" s="9">
         <f t="shared" si="0"/>
-        <v>0.80609377311048658</v>
+        <v>1</v>
       </c>
       <c r="N9" s="10">
         <f t="shared" si="1"/>
-        <v>-520</v>
+        <v>-502</v>
       </c>
       <c r="O9" s="11">
         <f t="shared" si="2"/>
-        <v>-0.28888888888888886</v>
+        <v>-0.27888888888888891</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -1664,7 +1670,7 @@
         <v>64.239999999999995</v>
       </c>
       <c r="L10" s="1">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="M10" s="9">
         <f t="shared" si="0"/>
@@ -1672,11 +1678,11 @@
       </c>
       <c r="N10" s="10">
         <f t="shared" si="1"/>
-        <v>-447</v>
+        <v>-445</v>
       </c>
       <c r="O10" s="11">
         <f t="shared" si="2"/>
-        <v>-0.24833333333333332</v>
+        <v>-0.24722222222222223</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -1714,7 +1720,7 @@
         <v>29.89</v>
       </c>
       <c r="L11" s="1">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="M11" s="9">
         <f t="shared" si="0"/>
@@ -1722,11 +1728,11 @@
       </c>
       <c r="N11" s="10">
         <f t="shared" si="1"/>
-        <v>-416</v>
+        <v>-408</v>
       </c>
       <c r="O11" s="11">
         <f t="shared" si="2"/>
-        <v>-0.2311111111111111</v>
+        <v>-0.22666666666666666</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2160,7 +2166,7 @@
         <v>58.59</v>
       </c>
       <c r="L21" s="1">
-        <v>1042</v>
+        <v>1250</v>
       </c>
       <c r="M21" s="9">
         <f t="shared" si="0"/>
@@ -2168,11 +2174,11 @@
       </c>
       <c r="N21" s="10">
         <f t="shared" si="1"/>
-        <v>-658</v>
+        <v>-450</v>
       </c>
       <c r="O21" s="11">
         <f t="shared" si="2"/>
-        <v>-0.38705882352941179</v>
+        <v>-0.26470588235294118</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2260,7 +2266,7 @@
         <v>63.11</v>
       </c>
       <c r="L23" s="1">
-        <v>1140</v>
+        <v>1000</v>
       </c>
       <c r="M23" s="9">
         <f t="shared" si="0"/>
@@ -2268,11 +2274,11 @@
       </c>
       <c r="N23" s="10">
         <f t="shared" si="1"/>
-        <v>-560</v>
+        <v>-700</v>
       </c>
       <c r="O23" s="11">
         <f t="shared" si="2"/>
-        <v>-0.32941176470588235</v>
+        <v>-0.41176470588235292</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2357,22 +2363,22 @@
         <v>1800</v>
       </c>
       <c r="K25" s="1">
-        <v>22.5</v>
+        <v>35.5</v>
       </c>
       <c r="L25" s="1">
-        <v>1400</v>
+        <v>1630</v>
       </c>
       <c r="M25" s="9">
         <f t="shared" si="0"/>
-        <v>0.33215234720992032</v>
+        <v>0.52406259226454088</v>
       </c>
       <c r="N25" s="10">
         <f t="shared" si="1"/>
-        <v>-400</v>
+        <v>-170</v>
       </c>
       <c r="O25" s="11">
         <f t="shared" si="2"/>
-        <v>-0.22222222222222221</v>
+        <v>-9.4444444444444442E-2</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2406,17 +2412,23 @@
       <c r="J26" s="1">
         <v>1800</v>
       </c>
+      <c r="K26" s="1">
+        <v>24.52</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1301</v>
+      </c>
       <c r="M26" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O26" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="N26" s="10">
+        <f t="shared" si="1"/>
+        <v>-499</v>
+      </c>
+      <c r="O26" s="11">
+        <f t="shared" si="2"/>
+        <v>-0.2772222222222222</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3158,17 +3170,23 @@
       <c r="J42" s="1">
         <v>2100</v>
       </c>
+      <c r="K42" s="1">
+        <v>44</v>
+      </c>
+      <c r="L42" s="1">
+        <v>2100</v>
+      </c>
       <c r="M42" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N42" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O42" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>0.18085412470713963</v>
+      </c>
+      <c r="N42" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O42" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3247,22 +3265,22 @@
         <v>2000</v>
       </c>
       <c r="K44" s="1">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="L44" s="1">
-        <v>2100</v>
+        <v>2230</v>
       </c>
       <c r="M44" s="9">
         <f t="shared" si="0"/>
-        <v>0.6909380813180972</v>
+        <v>0.95003986181238365</v>
       </c>
       <c r="N44" s="10">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="O44" s="11">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3362,15 +3380,15 @@
       </c>
       <c r="F49" s="17">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1663.5368918888914</v>
+        <v>1670.9781512978213</v>
       </c>
       <c r="G49" s="18">
         <f>IF(F49&lt;&gt;"",F49-E49,"")</f>
-        <v>-383.82905856665275</v>
+        <v>-376.38779915772284</v>
       </c>
       <c r="H49" s="19">
         <f>IF(AND(F49&lt;&gt;"",E49&gt;0),(F49-E49)/E49,"")</f>
-        <v>-0.18747457360089914</v>
+        <v>-0.18384002091759688</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3383,11 +3401,11 @@
       </c>
       <c r="C50" s="20">
         <f>SUMIF(F$2:F$45,"Sj2",K$2:K$45)</f>
-        <v>1171.7399999999998</v>
+        <v>1374.3999999999999</v>
       </c>
       <c r="D50" s="21">
         <f>IF(B50&gt;0,C50/B50,"")</f>
-        <v>0.28747089692666633</v>
+        <v>0.33719084501340763</v>
       </c>
       <c r="E50" s="22">
         <f>IF(SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMIF(F$2:F$45,"Sj2",C$2:C$45),"")</f>
@@ -3395,15 +3413,15 @@
       </c>
       <c r="F50" s="22">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1563.3080973594826</v>
+        <v>1605.2783396391153</v>
       </c>
       <c r="G50" s="23">
         <f>IF(F50&lt;&gt;"",F50-E50,"")</f>
-        <v>-374.59078954763027</v>
+        <v>-332.62054726799761</v>
       </c>
       <c r="H50" s="24">
         <f>IF(AND(F50&lt;&gt;"",E50&gt;0),(F50-E50)/E50,"")</f>
-        <v>-0.19329738619411524</v>
+        <v>-0.17163978446721753</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3416,11 +3434,11 @@
       </c>
       <c r="C51" s="26">
         <f>SUM(C49:C50)</f>
-        <v>1622.11</v>
+        <v>1824.77</v>
       </c>
       <c r="D51" s="27">
         <f>IF(B51&gt;0,C51/B51,"")</f>
-        <v>0.35692344929258246</v>
+        <v>0.40151605166457627</v>
       </c>
       <c r="E51" s="28">
         <f>IF(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)),"")</f>
@@ -3428,15 +3446,15 @@
       </c>
       <c r="F51" s="28">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1591.1360758518222</v>
+        <v>1621.4936567348211</v>
       </c>
       <c r="G51" s="29">
         <f>IF(F51&lt;&gt;"",F51-E51,"")</f>
-        <v>-358.05154929395167</v>
+        <v>-327.69396841095272</v>
       </c>
       <c r="H51" s="30">
         <f>IF(AND(F51&lt;&gt;"",E51&gt;0),(F51-E51)/E51,"")</f>
-        <v>-0.18369270596368273</v>
+        <v>-0.1681182274007334</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3534,15 +3552,15 @@
       </c>
       <c r="G56" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1237.8057682180904</v>
+        <v>1251.3810102483089</v>
       </c>
       <c r="H56" s="51">
         <f t="shared" si="4"/>
-        <v>-462.19423178190959</v>
+        <v>-448.61898975169106</v>
       </c>
       <c r="I56" s="52">
         <f t="shared" si="5"/>
-        <v>-0.27187895987171151</v>
+        <v>-0.26389352338334771</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3558,11 +3576,11 @@
       </c>
       <c r="D57" s="42">
         <f>SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>498.82</v>
+        <v>580.95999999999992</v>
       </c>
       <c r="E57" s="43">
         <f t="shared" si="3"/>
-        <v>0.64857625796385387</v>
+        <v>0.75537641399037825</v>
       </c>
       <c r="F57" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3570,15 +3588,15 @@
       </c>
       <c r="G57" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1475.3939898159658</v>
+        <v>1479.111178050124</v>
       </c>
       <c r="H57" s="45">
         <f t="shared" si="4"/>
-        <v>-324.60601018403418</v>
+        <v>-320.88882194987605</v>
       </c>
       <c r="I57" s="46">
         <f t="shared" si="5"/>
-        <v>-0.18033667232446343</v>
+        <v>-0.17827156774993114</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3666,11 +3684,11 @@
       </c>
       <c r="D60" s="48">
         <f>SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>22.5</v>
+        <v>60.019999999999996</v>
       </c>
       <c r="E60" s="49">
         <f t="shared" si="3"/>
-        <v>0.14127841265854579</v>
+        <v>0.37686801456737412</v>
       </c>
       <c r="F60" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3678,15 +3696,15 @@
       </c>
       <c r="G60" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1400</v>
+        <v>1495.5934688437189</v>
       </c>
       <c r="H60" s="51">
         <f t="shared" si="4"/>
-        <v>-400</v>
+        <v>-304.40653115628106</v>
       </c>
       <c r="I60" s="52">
         <f t="shared" si="5"/>
-        <v>-0.22222222222222221</v>
+        <v>-0.16911473953126727</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3774,11 +3792,11 @@
       </c>
       <c r="D63" s="42">
         <f>SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>243</v>
+        <v>326</v>
       </c>
       <c r="E63" s="43">
         <f t="shared" si="3"/>
-        <v>0.13223122507060495</v>
+        <v>0.1773966229342272</v>
       </c>
       <c r="F63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3786,15 +3804,15 @@
       </c>
       <c r="G63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1928.3950617283951</v>
+        <v>2029.1104294478528</v>
       </c>
       <c r="H63" s="45">
         <f t="shared" si="4"/>
-        <v>-130.05984633553294</v>
+        <v>-29.344478616075321</v>
       </c>
       <c r="I63" s="46">
         <f t="shared" si="5"/>
-        <v>-6.3183237983998511E-2</v>
+        <v>-1.4255584856932891E-2</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3808,11 +3826,11 @@
       </c>
       <c r="D64" s="55">
         <f>SUM(D55:D63)</f>
-        <v>1622.1100000000001</v>
+        <v>1824.77</v>
       </c>
       <c r="E64" s="56">
         <f t="shared" si="3"/>
-        <v>0.35692344929258263</v>
+        <v>0.40151605166457632</v>
       </c>
       <c r="F64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45),"")</f>
@@ -3820,15 +3838,15 @@
       </c>
       <c r="G64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1591.1360758518222</v>
+        <v>1621.4936567348211</v>
       </c>
       <c r="H64" s="58">
         <f t="shared" si="4"/>
-        <v>-358.05154929395212</v>
+        <v>-327.69396841095318</v>
       </c>
       <c r="I64" s="59">
         <f t="shared" si="5"/>
-        <v>-0.18369270596368292</v>
+        <v>-0.16811822740073359</v>
       </c>
     </row>
   </sheetData>

--- a/avance.xlsx
+++ b/avance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6BCE2DB-7277-475D-BCE7-ACA0B9FBEC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861EBC91-359E-421C-9860-6A2415F54ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1317,22 +1317,22 @@
         <v>1800</v>
       </c>
       <c r="K3" s="1">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="L3" s="1">
-        <v>2560</v>
+        <v>1820</v>
       </c>
       <c r="M3" s="9">
         <f t="shared" si="0"/>
-        <v>0.16279069767441862</v>
+        <v>0.69767441860465118</v>
       </c>
       <c r="N3" s="10">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>20</v>
       </c>
       <c r="O3" s="11">
         <f t="shared" si="2"/>
-        <v>0.42222222222222222</v>
+        <v>1.1111111111111112E-2</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2363,22 +2363,22 @@
         <v>1800</v>
       </c>
       <c r="K25" s="1">
-        <v>35.5</v>
+        <v>67.739999999999995</v>
       </c>
       <c r="L25" s="1">
-        <v>1630</v>
+        <v>1722</v>
       </c>
       <c r="M25" s="9">
         <f t="shared" si="0"/>
-        <v>0.52406259226454088</v>
+        <v>1</v>
       </c>
       <c r="N25" s="10">
         <f t="shared" si="1"/>
-        <v>-170</v>
+        <v>-78</v>
       </c>
       <c r="O25" s="11">
         <f t="shared" si="2"/>
-        <v>-9.4444444444444442E-2</v>
+        <v>-4.3333333333333335E-2</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2416,7 +2416,7 @@
         <v>24.52</v>
       </c>
       <c r="L26" s="1">
-        <v>1301</v>
+        <v>1220</v>
       </c>
       <c r="M26" s="9">
         <f t="shared" si="0"/>
@@ -2424,11 +2424,11 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="1"/>
-        <v>-499</v>
+        <v>-580</v>
       </c>
       <c r="O26" s="11">
         <f t="shared" si="2"/>
-        <v>-0.2772222222222222</v>
+        <v>-0.32222222222222224</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2463,22 +2463,22 @@
         <v>1700</v>
       </c>
       <c r="K27" s="1">
-        <v>12.7</v>
+        <v>31</v>
       </c>
       <c r="L27" s="1">
-        <v>1400</v>
+        <v>1120</v>
       </c>
       <c r="M27" s="9">
         <f t="shared" si="0"/>
-        <v>0.4096774193548387</v>
+        <v>1</v>
       </c>
       <c r="N27" s="10">
         <f t="shared" si="1"/>
-        <v>-300</v>
+        <v>-580</v>
       </c>
       <c r="O27" s="11">
         <f t="shared" si="2"/>
-        <v>-0.17647058823529413</v>
+        <v>-0.3411764705882353</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2800,17 +2800,23 @@
       <c r="J34" s="1">
         <v>1800</v>
       </c>
+      <c r="K34" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="L34" s="1">
+        <v>1500</v>
+      </c>
       <c r="M34" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N34" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O34" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>0.6026862587533004</v>
+      </c>
+      <c r="N34" s="10">
+        <f t="shared" si="1"/>
+        <v>-300</v>
+      </c>
+      <c r="O34" s="11">
+        <f t="shared" si="2"/>
+        <v>-0.16666666666666666</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3171,14 +3177,14 @@
         <v>2100</v>
       </c>
       <c r="K42" s="1">
-        <v>44</v>
+        <v>160</v>
       </c>
       <c r="L42" s="1">
         <v>2100</v>
       </c>
       <c r="M42" s="9">
         <f t="shared" si="0"/>
-        <v>0.18085412470713963</v>
+        <v>0.65765136257141688</v>
       </c>
       <c r="N42" s="10">
         <f t="shared" si="1"/>
@@ -3368,11 +3374,11 @@
       </c>
       <c r="C49" s="15">
         <f>SUMIF(F$2:F$45,"Sj1",K$2:K$45)</f>
-        <v>450.37000000000006</v>
+        <v>468.67000000000007</v>
       </c>
       <c r="D49" s="16">
         <f>IF(B49&gt;0,C49/B49,"")</f>
-        <v>0.96095333603601685</v>
+        <v>1</v>
       </c>
       <c r="E49" s="17">
         <f>IF(SUMIF(F$2:F$45,"Sj1",C$2:C$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj1")*C$2:C$45*J$2:J$45)/SUMIF(F$2:F$45,"Sj1",C$2:C$45),"")</f>
@@ -3380,15 +3386,15 @@
       </c>
       <c r="F49" s="17">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1670.9781512978213</v>
+        <v>1641.8768643181766</v>
       </c>
       <c r="G49" s="18">
         <f>IF(F49&lt;&gt;"",F49-E49,"")</f>
-        <v>-376.38779915772284</v>
+        <v>-405.48908613736762</v>
       </c>
       <c r="H49" s="19">
         <f>IF(AND(F49&lt;&gt;"",E49&gt;0),(F49-E49)/E49,"")</f>
-        <v>-0.18384002091759688</v>
+        <v>-0.19805403428104548</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3401,11 +3407,11 @@
       </c>
       <c r="C50" s="20">
         <f>SUMIF(F$2:F$45,"Sj2",K$2:K$45)</f>
-        <v>1374.3999999999999</v>
+        <v>1690.1399999999999</v>
       </c>
       <c r="D50" s="21">
         <f>IF(B50&gt;0,C50/B50,"")</f>
-        <v>0.33719084501340763</v>
+        <v>0.41465347409121123</v>
       </c>
       <c r="E50" s="22">
         <f>IF(SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMIF(F$2:F$45,"Sj2",C$2:C$45),"")</f>
@@ -3413,15 +3419,15 @@
       </c>
       <c r="F50" s="22">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1605.2783396391153</v>
+        <v>1638.2321641994156</v>
       </c>
       <c r="G50" s="23">
         <f>IF(F50&lt;&gt;"",F50-E50,"")</f>
-        <v>-332.62054726799761</v>
+        <v>-299.66672270769732</v>
       </c>
       <c r="H50" s="24">
         <f>IF(AND(F50&lt;&gt;"",E50&gt;0),(F50-E50)/E50,"")</f>
-        <v>-0.17163978446721753</v>
+        <v>-0.15463485981250832</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3434,11 +3440,11 @@
       </c>
       <c r="C51" s="26">
         <f>SUM(C49:C50)</f>
-        <v>1824.77</v>
+        <v>2158.81</v>
       </c>
       <c r="D51" s="27">
         <f>IF(B51&gt;0,C51/B51,"")</f>
-        <v>0.40151605166457627</v>
+        <v>0.47501705283076984</v>
       </c>
       <c r="E51" s="28">
         <f>IF(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)),"")</f>
@@ -3446,15 +3452,15 @@
       </c>
       <c r="F51" s="28">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1621.4936567348211</v>
+        <v>1639.0234156780816</v>
       </c>
       <c r="G51" s="29">
         <f>IF(F51&lt;&gt;"",F51-E51,"")</f>
-        <v>-327.69396841095272</v>
+        <v>-310.16420946769222</v>
       </c>
       <c r="H51" s="30">
         <f>IF(AND(F51&lt;&gt;"",E51&gt;0),(F51-E51)/E51,"")</f>
-        <v>-0.1681182274007334</v>
+        <v>-0.15912486077090499</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3540,11 +3546,11 @@
       </c>
       <c r="D56" s="48">
         <f>SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*K$2:K$45)</f>
-        <v>246.87</v>
+        <v>265.17</v>
       </c>
       <c r="E56" s="49">
         <f t="shared" si="3"/>
-        <v>0.93098766828826784</v>
+        <v>1</v>
       </c>
       <c r="F56" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*C$2:C$45),"")</f>
@@ -3552,15 +3558,15 @@
       </c>
       <c r="G56" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1251.3810102483089</v>
+        <v>1228.9038352754837</v>
       </c>
       <c r="H56" s="51">
         <f t="shared" si="4"/>
-        <v>-448.61898975169106</v>
+        <v>-471.09616472451626</v>
       </c>
       <c r="I56" s="52">
         <f t="shared" si="5"/>
-        <v>-0.26389352338334771</v>
+        <v>-0.27711539101442134</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3576,11 +3582,11 @@
       </c>
       <c r="D57" s="42">
         <f>SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>580.95999999999992</v>
+        <v>695.95999999999992</v>
       </c>
       <c r="E57" s="43">
         <f t="shared" si="3"/>
-        <v>0.75537641399037825</v>
+        <v>0.90490183331166285</v>
       </c>
       <c r="F57" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3588,15 +3594,15 @@
       </c>
       <c r="G57" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1479.111178050124</v>
+        <v>1498.2246537157309</v>
       </c>
       <c r="H57" s="45">
         <f t="shared" si="4"/>
-        <v>-320.88882194987605</v>
+        <v>-301.77534628426906</v>
       </c>
       <c r="I57" s="46">
         <f t="shared" si="5"/>
-        <v>-0.17827156774993114</v>
+        <v>-0.16765297015792727</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3684,11 +3690,11 @@
       </c>
       <c r="D60" s="48">
         <f>SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>60.019999999999996</v>
+        <v>92.259999999999991</v>
       </c>
       <c r="E60" s="49">
         <f t="shared" si="3"/>
-        <v>0.37686801456737412</v>
+        <v>0.57930428230566366</v>
       </c>
       <c r="F60" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3696,15 +3702,15 @@
       </c>
       <c r="G60" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1495.5934688437189</v>
+        <v>1588.5831346195534</v>
       </c>
       <c r="H60" s="51">
         <f t="shared" si="4"/>
-        <v>-304.40653115628106</v>
+        <v>-211.41686538044655</v>
       </c>
       <c r="I60" s="52">
         <f t="shared" si="5"/>
-        <v>-0.16911473953126727</v>
+        <v>-0.11745381410024809</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3756,11 +3762,11 @@
       </c>
       <c r="D62" s="48">
         <f>SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>407.42</v>
+        <v>459.92</v>
       </c>
       <c r="E62" s="49">
         <f t="shared" si="3"/>
-        <v>0.82393625626921208</v>
+        <v>0.93010839669956313</v>
       </c>
       <c r="F62" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3768,15 +3774,15 @@
       </c>
       <c r="G62" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1462.2124588876343</v>
+        <v>1466.5259175508784</v>
       </c>
       <c r="H62" s="51">
         <f t="shared" si="4"/>
-        <v>-460.22929810961523</v>
+        <v>-455.91583944637114</v>
       </c>
       <c r="I62" s="52">
         <f t="shared" si="5"/>
-        <v>-0.23939830501209494</v>
+        <v>-0.23715456543062566</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3792,11 +3798,11 @@
       </c>
       <c r="D63" s="42">
         <f>SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>326</v>
+        <v>442</v>
       </c>
       <c r="E63" s="43">
         <f t="shared" si="3"/>
-        <v>0.1773966229342272</v>
+        <v>0.24051934765928965</v>
       </c>
       <c r="F63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3804,15 +3810,15 @@
       </c>
       <c r="G63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>2029.1104294478528</v>
+        <v>2047.7149321266968</v>
       </c>
       <c r="H63" s="45">
         <f t="shared" si="4"/>
-        <v>-29.344478616075321</v>
+        <v>-10.739975937231293</v>
       </c>
       <c r="I63" s="46">
         <f t="shared" si="5"/>
-        <v>-1.4255584856932891E-2</v>
+        <v>-5.2174939053354031E-3</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3826,11 +3832,11 @@
       </c>
       <c r="D64" s="55">
         <f>SUM(D55:D63)</f>
-        <v>1824.77</v>
+        <v>2158.81</v>
       </c>
       <c r="E64" s="56">
         <f t="shared" si="3"/>
-        <v>0.40151605166457632</v>
+        <v>0.47501705283076989</v>
       </c>
       <c r="F64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45),"")</f>
@@ -3838,15 +3844,15 @@
       </c>
       <c r="G64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1621.4936567348211</v>
+        <v>1639.0234156780816</v>
       </c>
       <c r="H64" s="58">
         <f t="shared" si="4"/>
-        <v>-327.69396841095318</v>
+        <v>-310.16420946769267</v>
       </c>
       <c r="I64" s="59">
         <f t="shared" si="5"/>
-        <v>-0.16811822740073359</v>
+        <v>-0.15912486077090518</v>
       </c>
     </row>
   </sheetData>

--- a/avance.xlsx
+++ b/avance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861EBC91-359E-421C-9860-6A2415F54ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1B776E-9442-4CC1-98F1-C8AEFE5EA92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1317,22 +1317,22 @@
         <v>1800</v>
       </c>
       <c r="K3" s="1">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="L3" s="1">
-        <v>1820</v>
+        <v>1650</v>
       </c>
       <c r="M3" s="9">
         <f t="shared" si="0"/>
-        <v>0.69767441860465118</v>
+        <v>1</v>
       </c>
       <c r="N3" s="10">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>-150</v>
       </c>
       <c r="O3" s="11">
         <f t="shared" si="2"/>
-        <v>1.1111111111111112E-2</v>
+        <v>-8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -1367,22 +1367,22 @@
         <v>1800</v>
       </c>
       <c r="K4" s="1">
-        <v>38</v>
+        <v>46.14</v>
       </c>
       <c r="L4" s="1">
-        <v>2020</v>
+        <v>2075</v>
       </c>
       <c r="M4" s="9">
         <f t="shared" si="0"/>
-        <v>0.82358040745557004</v>
+        <v>1</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>275</v>
       </c>
       <c r="O4" s="11">
         <f t="shared" si="2"/>
-        <v>0.12222222222222222</v>
+        <v>0.15277777777777779</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2466,7 +2466,7 @@
         <v>31</v>
       </c>
       <c r="L27" s="1">
-        <v>1120</v>
+        <v>1000</v>
       </c>
       <c r="M27" s="9">
         <f t="shared" si="0"/>
@@ -2474,11 +2474,11 @@
       </c>
       <c r="N27" s="10">
         <f t="shared" si="1"/>
-        <v>-580</v>
+        <v>-700</v>
       </c>
       <c r="O27" s="11">
         <f t="shared" si="2"/>
-        <v>-0.3411764705882353</v>
+        <v>-0.41176470588235292</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2512,17 +2512,23 @@
       <c r="J28" s="1">
         <v>1800</v>
       </c>
+      <c r="K28" s="1">
+        <v>67</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1351</v>
+      </c>
       <c r="M28" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N28" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O28" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="N28" s="10">
+        <f t="shared" si="1"/>
+        <v>-449</v>
+      </c>
+      <c r="O28" s="11">
+        <f t="shared" si="2"/>
+        <v>-0.24944444444444444</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2754,7 +2760,7 @@
         <v>102.7</v>
       </c>
       <c r="L33" s="1">
-        <v>1520</v>
+        <v>1430</v>
       </c>
       <c r="M33" s="9">
         <f t="shared" si="0"/>
@@ -2762,11 +2768,11 @@
       </c>
       <c r="N33" s="10">
         <f t="shared" si="1"/>
-        <v>-480</v>
+        <v>-570</v>
       </c>
       <c r="O33" s="11">
         <f t="shared" si="2"/>
-        <v>-0.24</v>
+        <v>-0.28499999999999998</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2801,22 +2807,22 @@
         <v>1800</v>
       </c>
       <c r="K34" s="1">
-        <v>52.5</v>
+        <v>87.11</v>
       </c>
       <c r="L34" s="1">
-        <v>1500</v>
+        <v>1380</v>
       </c>
       <c r="M34" s="9">
         <f t="shared" si="0"/>
-        <v>0.6026862587533004</v>
+        <v>1</v>
       </c>
       <c r="N34" s="10">
         <f t="shared" si="1"/>
-        <v>-300</v>
+        <v>-420</v>
       </c>
       <c r="O34" s="11">
         <f t="shared" si="2"/>
-        <v>-0.16666666666666666</v>
+        <v>-0.23333333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3039,22 +3045,22 @@
         <v>2000</v>
       </c>
       <c r="K39" s="1">
-        <v>139</v>
+        <v>284</v>
       </c>
       <c r="L39" s="1">
-        <v>1800</v>
+        <v>1640</v>
       </c>
       <c r="M39" s="9">
         <f t="shared" si="0"/>
-        <v>0.73254281949934119</v>
+        <v>1.4967061923583662</v>
       </c>
       <c r="N39" s="10">
         <f t="shared" si="1"/>
-        <v>-200</v>
+        <v>-360</v>
       </c>
       <c r="O39" s="11">
         <f t="shared" si="2"/>
-        <v>-0.1</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3177,22 +3183,22 @@
         <v>2100</v>
       </c>
       <c r="K42" s="1">
-        <v>160</v>
+        <v>243.29</v>
       </c>
       <c r="L42" s="1">
-        <v>2100</v>
+        <v>2282</v>
       </c>
       <c r="M42" s="9">
         <f t="shared" si="0"/>
-        <v>0.65765136257141688</v>
+        <v>1</v>
       </c>
       <c r="N42" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="O42" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.666666666666667E-2</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3271,22 +3277,22 @@
         <v>2000</v>
       </c>
       <c r="K44" s="1">
-        <v>143</v>
+        <v>150.52000000000001</v>
       </c>
       <c r="L44" s="1">
-        <v>2230</v>
+        <v>2116</v>
       </c>
       <c r="M44" s="9">
         <f t="shared" si="0"/>
-        <v>0.95003986181238365</v>
+        <v>1</v>
       </c>
       <c r="N44" s="10">
         <f t="shared" si="1"/>
-        <v>230</v>
+        <v>116</v>
       </c>
       <c r="O44" s="11">
         <f t="shared" si="2"/>
-        <v>0.115</v>
+        <v>5.8000000000000003E-2</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3386,15 +3392,15 @@
       </c>
       <c r="F49" s="17">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1641.8768643181766</v>
+        <v>1633.9395096763178</v>
       </c>
       <c r="G49" s="18">
         <f>IF(F49&lt;&gt;"",F49-E49,"")</f>
-        <v>-405.48908613736762</v>
+        <v>-413.42644077922637</v>
       </c>
       <c r="H49" s="19">
         <f>IF(AND(F49&lt;&gt;"",E49&gt;0),(F49-E49)/E49,"")</f>
-        <v>-0.19805403428104548</v>
+        <v>-0.20193089598234157</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3407,11 +3413,11 @@
       </c>
       <c r="C50" s="20">
         <f>SUMIF(F$2:F$45,"Sj2",K$2:K$45)</f>
-        <v>1690.1399999999999</v>
+        <v>2100.7000000000003</v>
       </c>
       <c r="D50" s="21">
         <f>IF(B50&gt;0,C50/B50,"")</f>
-        <v>0.41465347409121123</v>
+        <v>0.51537893489498365</v>
       </c>
       <c r="E50" s="22">
         <f>IF(SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMIF(F$2:F$45,"Sj2",C$2:C$45),"")</f>
@@ -3419,15 +3425,15 @@
       </c>
       <c r="F50" s="22">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1638.2321641994156</v>
+        <v>1631.2020326557811</v>
       </c>
       <c r="G50" s="23">
         <f>IF(F50&lt;&gt;"",F50-E50,"")</f>
-        <v>-299.66672270769732</v>
+        <v>-306.69685425133184</v>
       </c>
       <c r="H50" s="24">
         <f>IF(AND(F50&lt;&gt;"",E50&gt;0),(F50-E50)/E50,"")</f>
-        <v>-0.15463485981250832</v>
+        <v>-0.15826256794069379</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3440,11 +3446,11 @@
       </c>
       <c r="C51" s="26">
         <f>SUM(C49:C50)</f>
-        <v>2158.81</v>
+        <v>2569.3700000000003</v>
       </c>
       <c r="D51" s="27">
         <f>IF(B51&gt;0,C51/B51,"")</f>
-        <v>0.47501705283076984</v>
+        <v>0.56535524897132927</v>
       </c>
       <c r="E51" s="28">
         <f>IF(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)),"")</f>
@@ -3452,15 +3458,15 @@
       </c>
       <c r="F51" s="28">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1639.0234156780816</v>
+        <v>1631.7013664828341</v>
       </c>
       <c r="G51" s="29">
         <f>IF(F51&lt;&gt;"",F51-E51,"")</f>
-        <v>-310.16420946769222</v>
+        <v>-317.48625866293969</v>
       </c>
       <c r="H51" s="30">
         <f>IF(AND(F51&lt;&gt;"",E51&gt;0),(F51-E51)/E51,"")</f>
-        <v>-0.15912486077090499</v>
+        <v>-0.16288132274551859</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3558,15 +3564,15 @@
       </c>
       <c r="G56" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1228.9038352754837</v>
+        <v>1214.8750989930988</v>
       </c>
       <c r="H56" s="51">
         <f t="shared" si="4"/>
-        <v>-471.09616472451626</v>
+        <v>-485.12490100690115</v>
       </c>
       <c r="I56" s="52">
         <f t="shared" si="5"/>
-        <v>-0.27711539101442134</v>
+        <v>-0.28536758882758889</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3582,11 +3588,11 @@
       </c>
       <c r="D57" s="42">
         <f>SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>695.95999999999992</v>
+        <v>769.1</v>
       </c>
       <c r="E57" s="43">
         <f t="shared" si="3"/>
-        <v>0.90490183331166285</v>
+        <v>1</v>
       </c>
       <c r="F57" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3594,15 +3600,15 @@
       </c>
       <c r="G57" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1498.2246537157309</v>
+        <v>1486.7181510856844</v>
       </c>
       <c r="H57" s="45">
         <f t="shared" si="4"/>
-        <v>-301.77534628426906</v>
+        <v>-313.28184891431556</v>
       </c>
       <c r="I57" s="46">
         <f t="shared" si="5"/>
-        <v>-0.16765297015792727</v>
+        <v>-0.1740454716190642</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3690,11 +3696,11 @@
       </c>
       <c r="D60" s="48">
         <f>SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>92.259999999999991</v>
+        <v>159.26</v>
       </c>
       <c r="E60" s="49">
         <f t="shared" si="3"/>
-        <v>0.57930428230566366</v>
+        <v>1</v>
       </c>
       <c r="F60" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3702,15 +3708,15 @@
       </c>
       <c r="G60" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1588.5831346195534</v>
+        <v>1488.6329272887103</v>
       </c>
       <c r="H60" s="51">
         <f t="shared" si="4"/>
-        <v>-211.41686538044655</v>
+        <v>-311.36707271128967</v>
       </c>
       <c r="I60" s="52">
         <f t="shared" si="5"/>
-        <v>-0.11745381410024809</v>
+        <v>-0.17298170706182758</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3762,11 +3768,11 @@
       </c>
       <c r="D62" s="48">
         <f>SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>459.92</v>
+        <v>494.53000000000003</v>
       </c>
       <c r="E62" s="49">
         <f t="shared" si="3"/>
-        <v>0.93010839669956313</v>
+        <v>1.0001011163242195</v>
       </c>
       <c r="F62" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3774,15 +3780,15 @@
       </c>
       <c r="G62" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1466.5259175508784</v>
+        <v>1429.0405031039572</v>
       </c>
       <c r="H62" s="51">
         <f t="shared" si="4"/>
-        <v>-455.91583944637114</v>
+        <v>-493.40125389329228</v>
       </c>
       <c r="I62" s="52">
         <f t="shared" si="5"/>
-        <v>-0.23715456543062566</v>
+        <v>-0.25665342114913198</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3798,11 +3804,11 @@
       </c>
       <c r="D63" s="42">
         <f>SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>442</v>
+        <v>677.81</v>
       </c>
       <c r="E63" s="43">
         <f t="shared" si="3"/>
-        <v>0.24051934765928965</v>
+        <v>0.36883805211978077</v>
       </c>
       <c r="F63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3810,15 +3816,15 @@
       </c>
       <c r="G63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>2047.7149321266968</v>
+        <v>1976.1409539546485</v>
       </c>
       <c r="H63" s="45">
         <f t="shared" si="4"/>
-        <v>-10.739975937231293</v>
+        <v>-82.313954109279621</v>
       </c>
       <c r="I63" s="46">
         <f t="shared" si="5"/>
-        <v>-5.2174939053354031E-3</v>
+        <v>-3.9988223102103169E-2</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3832,11 +3838,11 @@
       </c>
       <c r="D64" s="55">
         <f>SUM(D55:D63)</f>
-        <v>2158.81</v>
+        <v>2569.37</v>
       </c>
       <c r="E64" s="56">
         <f t="shared" si="3"/>
-        <v>0.47501705283076989</v>
+        <v>0.56535524897132927</v>
       </c>
       <c r="F64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45),"")</f>
@@ -3844,15 +3850,15 @@
       </c>
       <c r="G64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1639.0234156780816</v>
+        <v>1631.7013664828341</v>
       </c>
       <c r="H64" s="58">
         <f t="shared" si="4"/>
-        <v>-310.16420946769267</v>
+        <v>-317.48625866294014</v>
       </c>
       <c r="I64" s="59">
         <f t="shared" si="5"/>
-        <v>-0.15912486077090518</v>
+        <v>-0.16288132274551878</v>
       </c>
     </row>
   </sheetData>

--- a/avance.xlsx
+++ b/avance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1B776E-9442-4CC1-98F1-C8AEFE5EA92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49253158-859D-4D4F-A42F-FA9C654DDAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Avance cosecha" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="114">
   <si>
     <t>Campo</t>
   </si>
@@ -1620,7 +1620,7 @@
         <v>270.44</v>
       </c>
       <c r="L9" s="1">
-        <v>1298</v>
+        <v>1284</v>
       </c>
       <c r="M9" s="9">
         <f t="shared" si="0"/>
@@ -1628,11 +1628,11 @@
       </c>
       <c r="N9" s="10">
         <f t="shared" si="1"/>
-        <v>-502</v>
+        <v>-516</v>
       </c>
       <c r="O9" s="11">
         <f t="shared" si="2"/>
-        <v>-0.27888888888888891</v>
+        <v>-0.28666666666666668</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2118,17 +2118,23 @@
       <c r="J20" s="1">
         <v>1900</v>
       </c>
+      <c r="K20" s="1">
+        <v>138</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1700</v>
+      </c>
       <c r="M20" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O20" s="11" t="str">
+        <v>0.72631578947368425</v>
+      </c>
+      <c r="N20" s="10">
+        <f t="shared" si="1"/>
+        <v>-200</v>
+      </c>
+      <c r="O20" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-0.10526315789473684</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2516,7 +2522,7 @@
         <v>67</v>
       </c>
       <c r="L28" s="1">
-        <v>1351</v>
+        <v>1240</v>
       </c>
       <c r="M28" s="9">
         <f t="shared" si="0"/>
@@ -2524,11 +2530,11 @@
       </c>
       <c r="N28" s="10">
         <f t="shared" si="1"/>
-        <v>-449</v>
+        <v>-560</v>
       </c>
       <c r="O28" s="11">
         <f t="shared" si="2"/>
-        <v>-0.24944444444444444</v>
+        <v>-0.31111111111111112</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2810,7 +2816,7 @@
         <v>87.11</v>
       </c>
       <c r="L34" s="1">
-        <v>1380</v>
+        <v>1387</v>
       </c>
       <c r="M34" s="9">
         <f t="shared" si="0"/>
@@ -2818,11 +2824,11 @@
       </c>
       <c r="N34" s="10">
         <f t="shared" si="1"/>
-        <v>-420</v>
+        <v>-413</v>
       </c>
       <c r="O34" s="11">
         <f t="shared" si="2"/>
-        <v>-0.23333333333333334</v>
+        <v>-0.22944444444444445</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3045,22 +3051,22 @@
         <v>2000</v>
       </c>
       <c r="K39" s="1">
-        <v>284</v>
+        <v>189.75</v>
       </c>
       <c r="L39" s="1">
-        <v>1640</v>
+        <v>1720</v>
       </c>
       <c r="M39" s="9">
         <f t="shared" si="0"/>
-        <v>1.4967061923583662</v>
+        <v>1</v>
       </c>
       <c r="N39" s="10">
         <f t="shared" si="1"/>
-        <v>-360</v>
+        <v>-280</v>
       </c>
       <c r="O39" s="11">
         <f t="shared" si="2"/>
-        <v>-0.18</v>
+        <v>-0.14000000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3094,17 +3100,23 @@
       <c r="J40" s="1">
         <v>2300</v>
       </c>
+      <c r="K40" s="1">
+        <v>106</v>
+      </c>
+      <c r="L40" s="1">
+        <v>2030</v>
+      </c>
       <c r="M40" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N40" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O40" s="11" t="str">
+        <v>0.62496315075762032</v>
+      </c>
+      <c r="N40" s="10">
+        <f t="shared" si="1"/>
+        <v>-270</v>
+      </c>
+      <c r="O40" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-0.11739130434782609</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3186,7 +3198,7 @@
         <v>243.29</v>
       </c>
       <c r="L42" s="1">
-        <v>2282</v>
+        <v>2297</v>
       </c>
       <c r="M42" s="9">
         <f t="shared" si="0"/>
@@ -3194,11 +3206,11 @@
       </c>
       <c r="N42" s="10">
         <f t="shared" si="1"/>
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="O42" s="11">
         <f t="shared" si="2"/>
-        <v>8.666666666666667E-2</v>
+        <v>9.3809523809523815E-2</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3413,11 +3425,11 @@
       </c>
       <c r="C50" s="20">
         <f>SUMIF(F$2:F$45,"Sj2",K$2:K$45)</f>
-        <v>2100.7000000000003</v>
+        <v>2250.4500000000003</v>
       </c>
       <c r="D50" s="21">
         <f>IF(B50&gt;0,C50/B50,"")</f>
-        <v>0.51537893489498365</v>
+        <v>0.55211811493045937</v>
       </c>
       <c r="E50" s="22">
         <f>IF(SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMIF(F$2:F$45,"Sj2",C$2:C$45),"")</f>
@@ -3425,15 +3437,15 @@
       </c>
       <c r="F50" s="22">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1631.2020326557811</v>
+        <v>1657.4872003377097</v>
       </c>
       <c r="G50" s="23">
         <f>IF(F50&lt;&gt;"",F50-E50,"")</f>
-        <v>-306.69685425133184</v>
+        <v>-280.41168656940317</v>
       </c>
       <c r="H50" s="24">
         <f>IF(AND(F50&lt;&gt;"",E50&gt;0),(F50-E50)/E50,"")</f>
-        <v>-0.15826256794069379</v>
+        <v>-0.1446988222470886</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3446,11 +3458,11 @@
       </c>
       <c r="C51" s="26">
         <f>SUM(C49:C50)</f>
-        <v>2569.3700000000003</v>
+        <v>2719.1200000000003</v>
       </c>
       <c r="D51" s="27">
         <f>IF(B51&gt;0,C51/B51,"")</f>
-        <v>0.56535524897132927</v>
+        <v>0.59830571874931238</v>
       </c>
       <c r="E51" s="28">
         <f>IF(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)),"")</f>
@@ -3458,15 +3470,15 @@
       </c>
       <c r="F51" s="28">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1631.7013664828341</v>
+        <v>1653.4284989261232</v>
       </c>
       <c r="G51" s="29">
         <f>IF(F51&lt;&gt;"",F51-E51,"")</f>
-        <v>-317.48625866293969</v>
+        <v>-295.75912621965062</v>
       </c>
       <c r="H51" s="30">
         <f>IF(AND(F51&lt;&gt;"",E51&gt;0),(F51-E51)/E51,"")</f>
-        <v>-0.16288132274551859</v>
+        <v>-0.15173455977463005</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3600,15 +3612,15 @@
       </c>
       <c r="G57" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1486.7181510856844</v>
+        <v>1481.795306202054</v>
       </c>
       <c r="H57" s="45">
         <f t="shared" si="4"/>
-        <v>-313.28184891431556</v>
+        <v>-318.20469379794599</v>
       </c>
       <c r="I57" s="46">
         <f t="shared" si="5"/>
-        <v>-0.1740454716190642</v>
+        <v>-0.17678038544330332</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3660,27 +3672,27 @@
       </c>
       <c r="D59" s="42">
         <f>SUMPRODUCT((A$2:A$45="Pereira")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="E59" s="43">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.45695364238410596</v>
       </c>
       <c r="F59" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Pereira")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Pereira")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Pereira")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
         <v>1900</v>
       </c>
-      <c r="G59" s="44" t="str">
+      <c r="G59" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Pereira")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Pereira")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Pereira")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v/>
-      </c>
-      <c r="H59" s="45" t="str">
+        <v>1700</v>
+      </c>
+      <c r="H59" s="45">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I59" s="46" t="str">
+        <v>-200</v>
+      </c>
+      <c r="I59" s="46">
         <f t="shared" si="5"/>
-        <v/>
+        <v>-0.10526315789473684</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3708,15 +3720,15 @@
       </c>
       <c r="G60" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1488.6329272887103</v>
+        <v>1441.9357026246389</v>
       </c>
       <c r="H60" s="51">
         <f t="shared" si="4"/>
-        <v>-311.36707271128967</v>
+        <v>-358.06429737536109</v>
       </c>
       <c r="I60" s="52">
         <f t="shared" si="5"/>
-        <v>-0.17298170706182758</v>
+        <v>-0.1989246096529784</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3780,15 +3792,15 @@
       </c>
       <c r="G62" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1429.0405031039572</v>
+        <v>1430.2735324449475</v>
       </c>
       <c r="H62" s="51">
         <f t="shared" si="4"/>
-        <v>-493.40125389329228</v>
+        <v>-492.16822455230204</v>
       </c>
       <c r="I62" s="52">
         <f t="shared" si="5"/>
-        <v>-0.25665342114913198</v>
+        <v>-0.2560120340504059</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3804,11 +3816,11 @@
       </c>
       <c r="D63" s="42">
         <f>SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>677.81</v>
+        <v>689.56</v>
       </c>
       <c r="E63" s="43">
         <f t="shared" si="3"/>
-        <v>0.36883805211978077</v>
+        <v>0.37523194880529354</v>
       </c>
       <c r="F63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3816,15 +3828,15 @@
       </c>
       <c r="G63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1976.1409539546485</v>
+        <v>2057.6707610650269</v>
       </c>
       <c r="H63" s="45">
         <f t="shared" si="4"/>
-        <v>-82.313954109279621</v>
+        <v>-0.78414699890117845</v>
       </c>
       <c r="I63" s="46">
         <f t="shared" si="5"/>
-        <v>-3.9988223102103169E-2</v>
+        <v>-3.8093960466625181E-4</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3838,11 +3850,11 @@
       </c>
       <c r="D64" s="55">
         <f>SUM(D55:D63)</f>
-        <v>2569.37</v>
+        <v>2719.12</v>
       </c>
       <c r="E64" s="56">
         <f t="shared" si="3"/>
-        <v>0.56535524897132927</v>
+        <v>0.59830571874931238</v>
       </c>
       <c r="F64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45),"")</f>
@@ -3850,15 +3862,15 @@
       </c>
       <c r="G64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1631.7013664828341</v>
+        <v>1653.4284989261232</v>
       </c>
       <c r="H64" s="58">
         <f t="shared" si="4"/>
-        <v>-317.48625866294014</v>
+        <v>-295.75912621965108</v>
       </c>
       <c r="I64" s="59">
         <f t="shared" si="5"/>
-        <v>-0.16288132274551878</v>
+        <v>-0.15173455977463027</v>
       </c>
     </row>
   </sheetData>
@@ -4548,17 +4560,26 @@
       <c r="D24" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="36"/>
+      <c r="E24" s="36">
+        <v>40</v>
+      </c>
       <c r="F24" s="37">
         <f t="shared" si="0"/>
-        <v>71.48</v>
+        <v>31.480000000000004</v>
       </c>
       <c r="G24" s="38">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
+        <v>0.55959709009513148</v>
+      </c>
+      <c r="H24" s="39">
+        <v>46157</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="25" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
@@ -5450,11 +5471,11 @@
       </c>
       <c r="C58" s="15">
         <f>SUMIF(D$2:D$55,"Cz",E$2:E$55)</f>
-        <v>757.18</v>
+        <v>797.18</v>
       </c>
       <c r="D58" s="16">
         <f>IF(B58&gt;0,C58/B58,"")</f>
-        <v>0.61767752987722802</v>
+        <v>0.65030794958600158</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5501,11 +5522,11 @@
       </c>
       <c r="C61" s="26">
         <f>SUM(C58:C60)</f>
-        <v>757.18</v>
+        <v>797.18</v>
       </c>
       <c r="D61" s="27">
         <f>IF(B61&gt;0,C61/B61,"")</f>
-        <v>0.24368092789145418</v>
+        <v>0.25655400578001192</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5603,11 +5624,11 @@
       </c>
       <c r="D68" s="20">
         <f>SUMPRODUCT((A$2:A$55="La Campana")*(D$2:D$55="Cz")*E$2:E$55)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E68" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.15084662669231058</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5681,11 +5702,11 @@
       </c>
       <c r="D72" s="26">
         <f>SUM(D65:D71)</f>
-        <v>757.18</v>
+        <v>797.18</v>
       </c>
       <c r="E72" s="27">
         <f t="shared" si="4"/>
-        <v>0.24368092789145418</v>
+        <v>0.25655400578001192</v>
       </c>
     </row>
   </sheetData>

--- a/avance.xlsx
+++ b/avance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49253158-859D-4D4F-A42F-FA9C654DDAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625C4B53-6090-4B06-B381-B2F4709EFF77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="114">
   <si>
     <t>Campo</t>
   </si>
@@ -2074,17 +2074,23 @@
       <c r="J19" s="1">
         <v>1900</v>
       </c>
+      <c r="K19" s="1">
+        <v>112</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1470</v>
+      </c>
       <c r="M19" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O19" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="N19" s="10">
+        <f t="shared" si="1"/>
+        <v>-430</v>
+      </c>
+      <c r="O19" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-0.22631578947368422</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2119,22 +2125,22 @@
         <v>1900</v>
       </c>
       <c r="K20" s="1">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="L20" s="1">
-        <v>1700</v>
+        <v>1470</v>
       </c>
       <c r="M20" s="9">
         <f t="shared" si="0"/>
-        <v>0.72631578947368425</v>
+        <v>1</v>
       </c>
       <c r="N20" s="10">
         <f t="shared" si="1"/>
-        <v>-200</v>
+        <v>-430</v>
       </c>
       <c r="O20" s="11">
         <f t="shared" si="2"/>
-        <v>-0.10526315789473684</v>
+        <v>-0.22631578947368422</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2568,17 +2574,23 @@
       <c r="J29" s="1">
         <v>1900</v>
       </c>
+      <c r="K29" s="1">
+        <v>91</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1910</v>
+      </c>
       <c r="M29" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N29" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O29" s="11" t="str">
+        <v>0.64220183486238536</v>
+      </c>
+      <c r="N29" s="10">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="O29" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5.263157894736842E-3</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2962,17 +2974,23 @@
       <c r="J37" s="1">
         <v>2200</v>
       </c>
+      <c r="K37" s="1">
+        <v>85</v>
+      </c>
+      <c r="L37" s="1">
+        <v>2110</v>
+      </c>
       <c r="M37" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N37" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O37" s="11" t="str">
+        <v>0.22009321595028483</v>
+      </c>
+      <c r="N37" s="10">
+        <f t="shared" si="1"/>
+        <v>-90</v>
+      </c>
+      <c r="O37" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-4.0909090909090909E-2</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3101,22 +3119,22 @@
         <v>2300</v>
       </c>
       <c r="K40" s="1">
-        <v>106</v>
+        <v>169.61</v>
       </c>
       <c r="L40" s="1">
-        <v>2030</v>
+        <v>1984</v>
       </c>
       <c r="M40" s="9">
         <f t="shared" si="0"/>
-        <v>0.62496315075762032</v>
+        <v>1</v>
       </c>
       <c r="N40" s="10">
         <f t="shared" si="1"/>
-        <v>-270</v>
+        <v>-316</v>
       </c>
       <c r="O40" s="11">
         <f t="shared" si="2"/>
-        <v>-0.11739130434782609</v>
+        <v>-0.13739130434782609</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3425,11 +3443,11 @@
       </c>
       <c r="C50" s="20">
         <f>SUMIF(F$2:F$45,"Sj2",K$2:K$45)</f>
-        <v>2250.4500000000003</v>
+        <v>2654.06</v>
       </c>
       <c r="D50" s="21">
         <f>IF(B50&gt;0,C50/B50,"")</f>
-        <v>0.55211811493045937</v>
+        <v>0.6511384852417671</v>
       </c>
       <c r="E50" s="22">
         <f>IF(SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMIF(F$2:F$45,"Sj2",C$2:C$45),"")</f>
@@ -3437,15 +3455,15 @@
       </c>
       <c r="F50" s="22">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1657.4872003377097</v>
+        <v>1663.0815844404422</v>
       </c>
       <c r="G50" s="23">
         <f>IF(F50&lt;&gt;"",F50-E50,"")</f>
-        <v>-280.41168656940317</v>
+        <v>-274.81730246667075</v>
       </c>
       <c r="H50" s="24">
         <f>IF(AND(F50&lt;&gt;"",E50&gt;0),(F50-E50)/E50,"")</f>
-        <v>-0.1446988222470886</v>
+        <v>-0.14181199252623508</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3458,11 +3476,11 @@
       </c>
       <c r="C51" s="26">
         <f>SUM(C49:C50)</f>
-        <v>2719.1200000000003</v>
+        <v>3122.73</v>
       </c>
       <c r="D51" s="27">
         <f>IF(B51&gt;0,C51/B51,"")</f>
-        <v>0.59830571874931238</v>
+        <v>0.68711466103373153</v>
       </c>
       <c r="E51" s="28">
         <f>IF(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)),"")</f>
@@ -3470,15 +3488,15 @@
       </c>
       <c r="F51" s="28">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1653.4284989261232</v>
+        <v>1658.7078421765568</v>
       </c>
       <c r="G51" s="29">
         <f>IF(F51&lt;&gt;"",F51-E51,"")</f>
-        <v>-295.75912621965062</v>
+        <v>-290.47978296921701</v>
       </c>
       <c r="H51" s="30">
         <f>IF(AND(F51&lt;&gt;"",E51&gt;0),(F51-E51)/E51,"")</f>
-        <v>-0.15173455977463005</v>
+        <v>-0.14902607590046285</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3672,11 +3690,11 @@
       </c>
       <c r="D59" s="42">
         <f>SUMPRODUCT((A$2:A$45="Pereira")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>138</v>
+        <v>302</v>
       </c>
       <c r="E59" s="43">
         <f t="shared" si="3"/>
-        <v>0.45695364238410596</v>
+        <v>1</v>
       </c>
       <c r="F59" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Pereira")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Pereira")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Pereira")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3684,15 +3702,15 @@
       </c>
       <c r="G59" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Pereira")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Pereira")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Pereira")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1700</v>
+        <v>1470</v>
       </c>
       <c r="H59" s="45">
         <f t="shared" si="4"/>
-        <v>-200</v>
+        <v>-430</v>
       </c>
       <c r="I59" s="46">
         <f t="shared" si="5"/>
-        <v>-0.10526315789473684</v>
+        <v>-0.22631578947368422</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3744,27 +3762,27 @@
       </c>
       <c r="D61" s="42">
         <f>SUMPRODUCT((A$2:A$45="San Luis")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="E61" s="43">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.64220183486238536</v>
       </c>
       <c r="F61" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="San Luis")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="San Luis")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="San Luis")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
         <v>1900.0000000000002</v>
       </c>
-      <c r="G61" s="44" t="str">
+      <c r="G61" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="San Luis")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="San Luis")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="San Luis")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v/>
-      </c>
-      <c r="H61" s="45" t="str">
+        <v>1910</v>
+      </c>
+      <c r="H61" s="45">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I61" s="46" t="str">
+        <v>9.9999999999997726</v>
+      </c>
+      <c r="I61" s="46">
         <f t="shared" si="5"/>
-        <v/>
+        <v>5.2631578947367214E-3</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3816,11 +3834,11 @@
       </c>
       <c r="D63" s="42">
         <f>SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>689.56</v>
+        <v>838.17</v>
       </c>
       <c r="E63" s="43">
         <f t="shared" si="3"/>
-        <v>0.37523194880529354</v>
+        <v>0.45609977743797919</v>
       </c>
       <c r="F63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3828,15 +3846,15 @@
       </c>
       <c r="G63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>2057.6707610650269</v>
+        <v>2051.5691208227449</v>
       </c>
       <c r="H63" s="45">
         <f t="shared" si="4"/>
-        <v>-0.78414699890117845</v>
+        <v>-6.8857872411831522</v>
       </c>
       <c r="I63" s="46">
         <f t="shared" si="5"/>
-        <v>-3.8093960466625181E-4</v>
+        <v>-3.3451241580314981E-3</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3850,11 +3868,11 @@
       </c>
       <c r="D64" s="55">
         <f>SUM(D55:D63)</f>
-        <v>2719.12</v>
+        <v>3122.73</v>
       </c>
       <c r="E64" s="56">
         <f t="shared" si="3"/>
-        <v>0.59830571874931238</v>
+        <v>0.68711466103373164</v>
       </c>
       <c r="F64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45),"")</f>
@@ -3862,15 +3880,15 @@
       </c>
       <c r="G64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1653.4284989261232</v>
+        <v>1658.7078421765568</v>
       </c>
       <c r="H64" s="58">
         <f t="shared" si="4"/>
-        <v>-295.75912621965108</v>
+        <v>-290.47978296921747</v>
       </c>
       <c r="I64" s="59">
         <f t="shared" si="5"/>
-        <v>-0.15173455977463027</v>
+        <v>-0.14902607590046305</v>
       </c>
     </row>
   </sheetData>
@@ -4561,15 +4579,15 @@
         <v>29</v>
       </c>
       <c r="E24" s="36">
-        <v>40</v>
+        <v>71.48</v>
       </c>
       <c r="F24" s="37">
         <f t="shared" si="0"/>
-        <v>31.480000000000004</v>
+        <v>0</v>
       </c>
       <c r="G24" s="38">
         <f t="shared" si="1"/>
-        <v>0.55959709009513148</v>
+        <v>1</v>
       </c>
       <c r="H24" s="39">
         <v>46157</v>
@@ -4656,17 +4674,26 @@
       <c r="D27" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E27" s="36"/>
+      <c r="E27" s="36">
+        <v>31</v>
+      </c>
       <c r="F27" s="37">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G27" s="38">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
+        <v>1</v>
+      </c>
+      <c r="H27" s="39">
+        <v>46158</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="28" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
@@ -5471,11 +5498,11 @@
       </c>
       <c r="C58" s="15">
         <f>SUMIF(D$2:D$55,"Cz",E$2:E$55)</f>
-        <v>797.18</v>
+        <v>859.66</v>
       </c>
       <c r="D58" s="16">
         <f>IF(B58&gt;0,C58/B58,"")</f>
-        <v>0.65030794958600158</v>
+        <v>0.70127666517110576</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5522,11 +5549,11 @@
       </c>
       <c r="C61" s="26">
         <f>SUM(C58:C60)</f>
-        <v>797.18</v>
+        <v>859.66</v>
       </c>
       <c r="D61" s="27">
         <f>IF(B61&gt;0,C61/B61,"")</f>
-        <v>0.25655400578001192</v>
+        <v>0.27666175344193916</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5624,11 +5651,11 @@
       </c>
       <c r="D68" s="20">
         <f>SUMPRODUCT((A$2:A$55="La Campana")*(D$2:D$55="Cz")*E$2:E$55)</f>
-        <v>40</v>
+        <v>102.48</v>
       </c>
       <c r="E68" s="21">
         <f t="shared" si="4"/>
-        <v>0.15084662669231058</v>
+        <v>0.38646905758569972</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5702,11 +5729,11 @@
       </c>
       <c r="D72" s="26">
         <f>SUM(D65:D71)</f>
-        <v>797.18</v>
+        <v>859.66</v>
       </c>
       <c r="E72" s="27">
         <f t="shared" si="4"/>
-        <v>0.25655400578001192</v>
+        <v>0.27666175344193916</v>
       </c>
     </row>
   </sheetData>

--- a/avance.xlsx
+++ b/avance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625C4B53-6090-4B06-B381-B2F4709EFF77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B384E0-7D14-43C4-B802-A918B931E221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="115">
   <si>
     <t>Campo</t>
   </si>
@@ -389,6 +389,9 @@
   </si>
   <si>
     <t>Cantidad</t>
+  </si>
+  <si>
+    <t>Nuola300</t>
   </si>
 </sst>
 </file>
@@ -1810,17 +1813,23 @@
       <c r="J13" s="1">
         <v>1800</v>
       </c>
+      <c r="K13" s="1">
+        <v>60.61</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1450</v>
+      </c>
       <c r="M13" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N13" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O13" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="N13" s="10">
+        <f t="shared" si="1"/>
+        <v>-350</v>
+      </c>
+      <c r="O13" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-0.19444444444444445</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -1854,17 +1863,23 @@
       <c r="J14" s="1">
         <v>1700</v>
       </c>
+      <c r="K14" s="1">
+        <v>56.69</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1250</v>
+      </c>
       <c r="M14" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O14" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="N14" s="10">
+        <f t="shared" si="1"/>
+        <v>-450</v>
+      </c>
+      <c r="O14" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-0.26470588235294118</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2975,22 +2990,22 @@
         <v>2200</v>
       </c>
       <c r="K37" s="1">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="L37" s="1">
-        <v>2110</v>
+        <v>2200</v>
       </c>
       <c r="M37" s="9">
         <f t="shared" si="0"/>
-        <v>0.22009321595028483</v>
+        <v>0.25375453133091663</v>
       </c>
       <c r="N37" s="10">
         <f t="shared" si="1"/>
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="O37" s="11">
         <f t="shared" si="2"/>
-        <v>-4.0909090909090909E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3443,11 +3458,11 @@
       </c>
       <c r="C50" s="20">
         <f>SUMIF(F$2:F$45,"Sj2",K$2:K$45)</f>
-        <v>2654.06</v>
+        <v>2784.36</v>
       </c>
       <c r="D50" s="21">
         <f>IF(B50&gt;0,C50/B50,"")</f>
-        <v>0.6511384852417671</v>
+        <v>0.68310586526595729</v>
       </c>
       <c r="E50" s="22">
         <f>IF(SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMIF(F$2:F$45,"Sj2",C$2:C$45),"")</f>
@@ -3455,15 +3470,15 @@
       </c>
       <c r="F50" s="22">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1663.0815844404422</v>
+        <v>1655.2871431855078</v>
       </c>
       <c r="G50" s="23">
         <f>IF(F50&lt;&gt;"",F50-E50,"")</f>
-        <v>-274.81730246667075</v>
+        <v>-282.61174372160508</v>
       </c>
       <c r="H50" s="24">
         <f>IF(AND(F50&lt;&gt;"",E50&gt;0),(F50-E50)/E50,"")</f>
-        <v>-0.14181199252623508</v>
+        <v>-0.14583410188787171</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3476,11 +3491,11 @@
       </c>
       <c r="C51" s="26">
         <f>SUM(C49:C50)</f>
-        <v>3122.73</v>
+        <v>3253.03</v>
       </c>
       <c r="D51" s="27">
         <f>IF(B51&gt;0,C51/B51,"")</f>
-        <v>0.68711466103373153</v>
+        <v>0.71578542037978299</v>
       </c>
       <c r="E51" s="28">
         <f>IF(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)),"")</f>
@@ -3488,15 +3503,15 @@
       </c>
       <c r="F51" s="28">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1658.7078421765568</v>
+        <v>1652.2115504621843</v>
       </c>
       <c r="G51" s="29">
         <f>IF(F51&lt;&gt;"",F51-E51,"")</f>
-        <v>-290.47978296921701</v>
+        <v>-296.97607468358956</v>
       </c>
       <c r="H51" s="30">
         <f>IF(AND(F51&lt;&gt;"",E51&gt;0),(F51-E51)/E51,"")</f>
-        <v>-0.14902607590046285</v>
+        <v>-0.15235889601001321</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3654,27 +3669,27 @@
       </c>
       <c r="D58" s="48">
         <f>SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>0</v>
+        <v>117.3</v>
       </c>
       <c r="E58" s="49">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.31549220010758477</v>
       </c>
       <c r="F58" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
         <v>1752.1382463690159</v>
       </c>
-      <c r="G58" s="50" t="str">
+      <c r="G58" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="51" t="str">
+        <v>1353.3418584825235</v>
+      </c>
+      <c r="H58" s="51">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I58" s="52" t="str">
+        <v>-398.79638788649231</v>
+      </c>
+      <c r="I58" s="52">
         <f t="shared" si="5"/>
-        <v/>
+        <v>-0.22760554922702272</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3834,11 +3849,11 @@
       </c>
       <c r="D63" s="42">
         <f>SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>838.17</v>
+        <v>851.17</v>
       </c>
       <c r="E63" s="43">
         <f t="shared" si="3"/>
-        <v>0.45609977743797919</v>
+        <v>0.46317387589854653</v>
       </c>
       <c r="F63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3846,15 +3861,15 @@
       </c>
       <c r="G63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>2051.5691208227449</v>
+        <v>2062.8237484873766</v>
       </c>
       <c r="H63" s="45">
         <f t="shared" si="4"/>
-        <v>-6.8857872411831522</v>
+        <v>4.3688404234485461</v>
       </c>
       <c r="I63" s="46">
         <f t="shared" si="5"/>
-        <v>-3.3451241580314981E-3</v>
+        <v>2.1223882079387602E-3</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3868,11 +3883,11 @@
       </c>
       <c r="D64" s="55">
         <f>SUM(D55:D63)</f>
-        <v>3122.73</v>
+        <v>3253.03</v>
       </c>
       <c r="E64" s="56">
         <f t="shared" si="3"/>
-        <v>0.68711466103373164</v>
+        <v>0.7157854203797831</v>
       </c>
       <c r="F64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45),"")</f>
@@ -3880,15 +3895,15 @@
       </c>
       <c r="G64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1658.7078421765568</v>
+        <v>1652.2115504621843</v>
       </c>
       <c r="H64" s="58">
         <f t="shared" si="4"/>
-        <v>-290.47978296921747</v>
+        <v>-296.97607468359001</v>
       </c>
       <c r="I64" s="59">
         <f t="shared" si="5"/>
-        <v>-0.14902607590046305</v>
+        <v>-0.1523588960100134</v>
       </c>
     </row>
   </sheetData>
@@ -4553,17 +4568,26 @@
       <c r="D23" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="36"/>
+      <c r="E23" s="36">
+        <v>50</v>
+      </c>
       <c r="F23" s="37">
         <f t="shared" si="0"/>
-        <v>63.11</v>
+        <v>13.11</v>
       </c>
       <c r="G23" s="38">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
+        <v>0.79226746949770244</v>
+      </c>
+      <c r="H23" s="39">
+        <v>46159</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="24" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
@@ -5498,11 +5522,11 @@
       </c>
       <c r="C58" s="15">
         <f>SUMIF(D$2:D$55,"Cz",E$2:E$55)</f>
-        <v>859.66</v>
+        <v>909.66</v>
       </c>
       <c r="D58" s="16">
         <f>IF(B58&gt;0,C58/B58,"")</f>
-        <v>0.70127666517110576</v>
+        <v>0.74206468980707263</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5549,11 +5573,11 @@
       </c>
       <c r="C61" s="26">
         <f>SUM(C58:C60)</f>
-        <v>859.66</v>
+        <v>909.66</v>
       </c>
       <c r="D61" s="27">
         <f>IF(B61&gt;0,C61/B61,"")</f>
-        <v>0.27666175344193916</v>
+        <v>0.29275310080263639</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5651,11 +5675,11 @@
       </c>
       <c r="D68" s="20">
         <f>SUMPRODUCT((A$2:A$55="La Campana")*(D$2:D$55="Cz")*E$2:E$55)</f>
-        <v>102.48</v>
+        <v>152.48000000000002</v>
       </c>
       <c r="E68" s="21">
         <f t="shared" si="4"/>
-        <v>0.38646905758569972</v>
+        <v>0.57502734095108798</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5729,11 +5753,11 @@
       </c>
       <c r="D72" s="26">
         <f>SUM(D65:D71)</f>
-        <v>859.66</v>
+        <v>909.66</v>
       </c>
       <c r="E72" s="27">
         <f t="shared" si="4"/>
-        <v>0.27666175344193916</v>
+        <v>0.29275310080263639</v>
       </c>
     </row>
   </sheetData>

--- a/avance.xlsx
+++ b/avance.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B384E0-7D14-43C4-B802-A918B931E221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Avance cosecha" sheetId="1" r:id="rId1"/>
@@ -3908,7 +3908,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O45" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" sqref="H2:H36" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>#REF!</formula1>
       <formula2>0</formula2>

--- a/avance.xlsx
+++ b/avance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B384E0-7D14-43C4-B802-A918B931E221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145B85A6-55A6-4A9E-85CA-5E705DC8E944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="115">
   <si>
     <t>Campo</t>
   </si>
@@ -1323,7 +1323,7 @@
         <v>215</v>
       </c>
       <c r="L3" s="1">
-        <v>1650</v>
+        <v>1792</v>
       </c>
       <c r="M3" s="9">
         <f t="shared" si="0"/>
@@ -1331,11 +1331,11 @@
       </c>
       <c r="N3" s="10">
         <f t="shared" si="1"/>
-        <v>-150</v>
+        <v>-8</v>
       </c>
       <c r="O3" s="11">
         <f t="shared" si="2"/>
-        <v>-8.3333333333333329E-2</v>
+        <v>-4.4444444444444444E-3</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -1769,17 +1769,23 @@
       <c r="J12" s="1">
         <v>1800</v>
       </c>
+      <c r="K12" s="1">
+        <v>52.63</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1153</v>
+      </c>
       <c r="M12" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O12" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="N12" s="10">
+        <f t="shared" si="1"/>
+        <v>-647</v>
+      </c>
+      <c r="O12" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-0.35944444444444446</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -1817,7 +1823,7 @@
         <v>60.61</v>
       </c>
       <c r="L13" s="1">
-        <v>1450</v>
+        <v>1362</v>
       </c>
       <c r="M13" s="9">
         <f t="shared" si="0"/>
@@ -1825,11 +1831,11 @@
       </c>
       <c r="N13" s="10">
         <f t="shared" si="1"/>
-        <v>-350</v>
+        <v>-438</v>
       </c>
       <c r="O13" s="11">
         <f t="shared" si="2"/>
-        <v>-0.19444444444444445</v>
+        <v>-0.24333333333333335</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -1867,7 +1873,7 @@
         <v>56.69</v>
       </c>
       <c r="L14" s="1">
-        <v>1250</v>
+        <v>1390</v>
       </c>
       <c r="M14" s="9">
         <f t="shared" si="0"/>
@@ -1875,11 +1881,11 @@
       </c>
       <c r="N14" s="10">
         <f t="shared" si="1"/>
-        <v>-450</v>
+        <v>-310</v>
       </c>
       <c r="O14" s="11">
         <f t="shared" si="2"/>
-        <v>-0.26470588235294118</v>
+        <v>-0.18235294117647058</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -1913,17 +1919,23 @@
       <c r="J15" s="1">
         <v>1800</v>
       </c>
+      <c r="K15" s="1">
+        <v>30</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1430</v>
+      </c>
       <c r="M15" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O15" s="11" t="str">
+        <v>0.60265166733627962</v>
+      </c>
+      <c r="N15" s="10">
+        <f t="shared" si="1"/>
+        <v>-370</v>
+      </c>
+      <c r="O15" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-0.20555555555555555</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2293,7 +2305,7 @@
         <v>63.11</v>
       </c>
       <c r="L23" s="1">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="M23" s="9">
         <f t="shared" si="0"/>
@@ -2301,11 +2313,11 @@
       </c>
       <c r="N23" s="10">
         <f t="shared" si="1"/>
-        <v>-700</v>
+        <v>-690</v>
       </c>
       <c r="O23" s="11">
         <f t="shared" si="2"/>
-        <v>-0.41176470588235292</v>
+        <v>-0.40588235294117647</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2393,7 +2405,7 @@
         <v>67.739999999999995</v>
       </c>
       <c r="L25" s="1">
-        <v>1722</v>
+        <v>1670</v>
       </c>
       <c r="M25" s="9">
         <f t="shared" si="0"/>
@@ -2401,11 +2413,11 @@
       </c>
       <c r="N25" s="10">
         <f t="shared" si="1"/>
-        <v>-78</v>
+        <v>-130</v>
       </c>
       <c r="O25" s="11">
         <f t="shared" si="2"/>
-        <v>-4.3333333333333335E-2</v>
+        <v>-7.2222222222222215E-2</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2543,7 +2555,7 @@
         <v>67</v>
       </c>
       <c r="L28" s="1">
-        <v>1240</v>
+        <v>1250</v>
       </c>
       <c r="M28" s="9">
         <f t="shared" si="0"/>
@@ -2551,11 +2563,11 @@
       </c>
       <c r="N28" s="10">
         <f t="shared" si="1"/>
-        <v>-560</v>
+        <v>-550</v>
       </c>
       <c r="O28" s="11">
         <f t="shared" si="2"/>
-        <v>-0.31111111111111112</v>
+        <v>-0.30555555555555558</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2590,22 +2602,22 @@
         <v>1900</v>
       </c>
       <c r="K29" s="1">
-        <v>91</v>
+        <v>141.69999999999999</v>
       </c>
       <c r="L29" s="1">
-        <v>1910</v>
+        <v>1920</v>
       </c>
       <c r="M29" s="9">
         <f t="shared" si="0"/>
-        <v>0.64220183486238536</v>
+        <v>1</v>
       </c>
       <c r="N29" s="10">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O29" s="11">
         <f t="shared" si="2"/>
-        <v>5.263157894736842E-3</v>
+        <v>1.0526315789473684E-2</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2843,7 +2855,7 @@
         <v>87.11</v>
       </c>
       <c r="L34" s="1">
-        <v>1387</v>
+        <v>1400</v>
       </c>
       <c r="M34" s="9">
         <f t="shared" si="0"/>
@@ -2851,11 +2863,11 @@
       </c>
       <c r="N34" s="10">
         <f t="shared" si="1"/>
-        <v>-413</v>
+        <v>-400</v>
       </c>
       <c r="O34" s="11">
         <f t="shared" si="2"/>
-        <v>-0.22944444444444445</v>
+        <v>-0.22222222222222221</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2943,7 +2955,7 @@
         <v>35.96</v>
       </c>
       <c r="L36" s="1">
-        <v>1671</v>
+        <v>1696</v>
       </c>
       <c r="M36" s="9">
         <f t="shared" si="0"/>
@@ -2951,11 +2963,11 @@
       </c>
       <c r="N36" s="10">
         <f t="shared" si="1"/>
-        <v>-329</v>
+        <v>-304</v>
       </c>
       <c r="O36" s="11">
         <f t="shared" si="2"/>
-        <v>-0.16450000000000001</v>
+        <v>-0.152</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2990,22 +3002,22 @@
         <v>2200</v>
       </c>
       <c r="K37" s="1">
-        <v>98</v>
+        <v>270</v>
       </c>
       <c r="L37" s="1">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="M37" s="9">
         <f t="shared" si="0"/>
-        <v>0.25375453133091663</v>
+        <v>0.69911962713619891</v>
       </c>
       <c r="N37" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="O37" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9.0909090909090912E-2</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3137,7 +3149,7 @@
         <v>169.61</v>
       </c>
       <c r="L40" s="1">
-        <v>1984</v>
+        <v>2000</v>
       </c>
       <c r="M40" s="9">
         <f t="shared" si="0"/>
@@ -3145,11 +3157,11 @@
       </c>
       <c r="N40" s="10">
         <f t="shared" si="1"/>
-        <v>-316</v>
+        <v>-300</v>
       </c>
       <c r="O40" s="11">
         <f t="shared" si="2"/>
-        <v>-0.13739130434782609</v>
+        <v>-0.13043478260869565</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3231,7 +3243,7 @@
         <v>243.29</v>
       </c>
       <c r="L42" s="1">
-        <v>2297</v>
+        <v>2300</v>
       </c>
       <c r="M42" s="9">
         <f t="shared" si="0"/>
@@ -3239,11 +3251,11 @@
       </c>
       <c r="N42" s="10">
         <f t="shared" si="1"/>
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="O42" s="11">
         <f t="shared" si="2"/>
-        <v>9.3809523809523815E-2</v>
+        <v>9.5238095238095233E-2</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3437,15 +3449,15 @@
       </c>
       <c r="F49" s="17">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1633.9395096763178</v>
+        <v>1635.2860861587042</v>
       </c>
       <c r="G49" s="18">
         <f>IF(F49&lt;&gt;"",F49-E49,"")</f>
-        <v>-413.42644077922637</v>
+        <v>-412.07986429684001</v>
       </c>
       <c r="H49" s="19">
         <f>IF(AND(F49&lt;&gt;"",E49&gt;0),(F49-E49)/E49,"")</f>
-        <v>-0.20193089598234157</v>
+        <v>-0.20127318431038241</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3458,11 +3470,11 @@
       </c>
       <c r="C50" s="20">
         <f>SUMIF(F$2:F$45,"Sj2",K$2:K$45)</f>
-        <v>2784.36</v>
+        <v>3089.69</v>
       </c>
       <c r="D50" s="21">
         <f>IF(B50&gt;0,C50/B50,"")</f>
-        <v>0.68310586526595729</v>
+        <v>0.75801453865648682</v>
       </c>
       <c r="E50" s="22">
         <f>IF(SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMIF(F$2:F$45,"Sj2",C$2:C$45),"")</f>
@@ -3470,15 +3482,15 @@
       </c>
       <c r="F50" s="22">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1655.2871431855078</v>
+        <v>1673.6006524926449</v>
       </c>
       <c r="G50" s="23">
         <f>IF(F50&lt;&gt;"",F50-E50,"")</f>
-        <v>-282.61174372160508</v>
+        <v>-264.29823441446797</v>
       </c>
       <c r="H50" s="24">
         <f>IF(AND(F50&lt;&gt;"",E50&gt;0),(F50-E50)/E50,"")</f>
-        <v>-0.14583410188787171</v>
+        <v>-0.13638391362940924</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3491,11 +3503,11 @@
       </c>
       <c r="C51" s="26">
         <f>SUM(C49:C50)</f>
-        <v>3253.03</v>
+        <v>3558.36</v>
       </c>
       <c r="D51" s="27">
         <f>IF(B51&gt;0,C51/B51,"")</f>
-        <v>0.71578542037978299</v>
+        <v>0.78296917288269841</v>
       </c>
       <c r="E51" s="28">
         <f>IF(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)),"")</f>
@@ -3503,15 +3515,15 @@
       </c>
       <c r="F51" s="28">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1652.2115504621843</v>
+        <v>1668.5542581413911</v>
       </c>
       <c r="G51" s="29">
         <f>IF(F51&lt;&gt;"",F51-E51,"")</f>
-        <v>-296.97607468358956</v>
+        <v>-280.63336700438276</v>
       </c>
       <c r="H51" s="30">
         <f>IF(AND(F51&lt;&gt;"",E51&gt;0),(F51-E51)/E51,"")</f>
-        <v>-0.15235889601001321</v>
+        <v>-0.14397452732822222</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3609,15 +3621,15 @@
       </c>
       <c r="G56" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj1")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1214.8750989930988</v>
+        <v>1217.2550816457367</v>
       </c>
       <c r="H56" s="51">
         <f t="shared" si="4"/>
-        <v>-485.12490100690115</v>
+        <v>-482.74491835426329</v>
       </c>
       <c r="I56" s="52">
         <f t="shared" si="5"/>
-        <v>-0.28536758882758889</v>
+        <v>-0.28396759903191959</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3645,15 +3657,15 @@
       </c>
       <c r="G57" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Malacara")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1481.795306202054</v>
+        <v>1521.491054479261</v>
       </c>
       <c r="H57" s="45">
         <f t="shared" si="4"/>
-        <v>-318.20469379794599</v>
+        <v>-278.50894552073896</v>
       </c>
       <c r="I57" s="46">
         <f t="shared" si="5"/>
-        <v>-0.17678038544330332</v>
+        <v>-0.1547271919559661</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3669,11 +3681,11 @@
       </c>
       <c r="D58" s="48">
         <f>SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>117.3</v>
+        <v>199.93</v>
       </c>
       <c r="E58" s="49">
         <f t="shared" si="3"/>
-        <v>0.31549220010758477</v>
+        <v>0.5377353415814955</v>
       </c>
       <c r="F58" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3681,15 +3693,15 @@
       </c>
       <c r="G58" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1353.3418584825235</v>
+        <v>1325.1253438703545</v>
       </c>
       <c r="H58" s="51">
         <f t="shared" si="4"/>
-        <v>-398.79638788649231</v>
+        <v>-427.01290249866133</v>
       </c>
       <c r="I58" s="52">
         <f t="shared" si="5"/>
-        <v>-0.22760554922702272</v>
+        <v>-0.24370959505254053</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3753,15 +3765,15 @@
       </c>
       <c r="G60" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="La Campana")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1441.9357026246389</v>
+        <v>1424.0248650006279</v>
       </c>
       <c r="H60" s="51">
         <f t="shared" si="4"/>
-        <v>-358.06429737536109</v>
+        <v>-375.97513499937213</v>
       </c>
       <c r="I60" s="52">
         <f t="shared" si="5"/>
-        <v>-0.1989246096529784</v>
+        <v>-0.20887507499965119</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3777,11 +3789,11 @@
       </c>
       <c r="D61" s="42">
         <f>SUMPRODUCT((A$2:A$45="San Luis")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>91</v>
+        <v>141.69999999999999</v>
       </c>
       <c r="E61" s="43">
         <f t="shared" si="3"/>
-        <v>0.64220183486238536</v>
+        <v>1</v>
       </c>
       <c r="F61" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="San Luis")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="San Luis")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="San Luis")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3789,15 +3801,15 @@
       </c>
       <c r="G61" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="San Luis")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="San Luis")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="San Luis")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1910</v>
+        <v>1920.0000000000002</v>
       </c>
       <c r="H61" s="45">
         <f t="shared" si="4"/>
-        <v>9.9999999999997726</v>
+        <v>20</v>
       </c>
       <c r="I61" s="46">
         <f t="shared" si="5"/>
-        <v>5.2631578947367214E-3</v>
+        <v>1.0526315789473682E-2</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3825,15 +3837,15 @@
       </c>
       <c r="G62" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="La Blanqueada")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1430.2735324449475</v>
+        <v>1434.3813317695588</v>
       </c>
       <c r="H62" s="51">
         <f t="shared" si="4"/>
-        <v>-492.16822455230204</v>
+        <v>-488.06042522769076</v>
       </c>
       <c r="I62" s="52">
         <f t="shared" si="5"/>
-        <v>-0.2560120340504059</v>
+        <v>-0.25387527265846266</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3849,11 +3861,11 @@
       </c>
       <c r="D63" s="42">
         <f>SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>851.17</v>
+        <v>1023.17</v>
       </c>
       <c r="E63" s="43">
         <f t="shared" si="3"/>
-        <v>0.46317387589854653</v>
+        <v>0.5567696401460529</v>
       </c>
       <c r="F63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3861,15 +3873,15 @@
       </c>
       <c r="G63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>2062.8237484873766</v>
+        <v>2036.4722577870737</v>
       </c>
       <c r="H63" s="45">
         <f t="shared" si="4"/>
-        <v>4.3688404234485461</v>
+        <v>-21.982650276854429</v>
       </c>
       <c r="I63" s="46">
         <f t="shared" si="5"/>
-        <v>2.1223882079387602E-3</v>
+        <v>-1.0679199330885574E-2</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3883,11 +3895,11 @@
       </c>
       <c r="D64" s="55">
         <f>SUM(D55:D63)</f>
-        <v>3253.03</v>
+        <v>3558.36</v>
       </c>
       <c r="E64" s="56">
         <f t="shared" si="3"/>
-        <v>0.7157854203797831</v>
+        <v>0.78296917288269863</v>
       </c>
       <c r="F64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45),"")</f>
@@ -3895,20 +3907,20 @@
       </c>
       <c r="G64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1652.2115504621843</v>
+        <v>1668.5542581413911</v>
       </c>
       <c r="H64" s="58">
         <f t="shared" si="4"/>
-        <v>-296.97607468359001</v>
+        <v>-280.63336700438322</v>
       </c>
       <c r="I64" s="59">
         <f t="shared" si="5"/>
-        <v>-0.1523588960100134</v>
+        <v>-0.14397452732822241</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O45" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H2:H36" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>#REF!</formula1>
       <formula2>0</formula2>
@@ -4518,17 +4530,26 @@
       <c r="D21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="36"/>
+      <c r="E21" s="36">
+        <v>58.59</v>
+      </c>
       <c r="F21" s="37">
         <f t="shared" si="0"/>
-        <v>58.59</v>
+        <v>0</v>
       </c>
       <c r="G21" s="38">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
+        <v>1</v>
+      </c>
+      <c r="H21" s="39">
+        <v>46160</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="22" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
@@ -5522,11 +5543,11 @@
       </c>
       <c r="C58" s="15">
         <f>SUMIF(D$2:D$55,"Cz",E$2:E$55)</f>
-        <v>909.66</v>
+        <v>968.24999999999989</v>
       </c>
       <c r="D58" s="16">
         <f>IF(B58&gt;0,C58/B58,"")</f>
-        <v>0.74206468980707263</v>
+        <v>0.78986009707549865</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5573,11 +5594,11 @@
       </c>
       <c r="C61" s="26">
         <f>SUM(C58:C60)</f>
-        <v>909.66</v>
+        <v>968.24999999999989</v>
       </c>
       <c r="D61" s="27">
         <f>IF(B61&gt;0,C61/B61,"")</f>
-        <v>0.29275310080263639</v>
+        <v>0.31160894163990133</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5675,11 +5696,11 @@
       </c>
       <c r="D68" s="20">
         <f>SUMPRODUCT((A$2:A$55="La Campana")*(D$2:D$55="Cz")*E$2:E$55)</f>
-        <v>152.48000000000002</v>
+        <v>211.07</v>
       </c>
       <c r="E68" s="21">
         <f t="shared" si="4"/>
-        <v>0.57502734095108798</v>
+        <v>0.79597993739864981</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5753,11 +5774,11 @@
       </c>
       <c r="D72" s="26">
         <f>SUM(D65:D71)</f>
-        <v>909.66</v>
+        <v>968.25</v>
       </c>
       <c r="E72" s="27">
         <f t="shared" si="4"/>
-        <v>0.29275310080263639</v>
+        <v>0.31160894163990138</v>
       </c>
     </row>
   </sheetData>

--- a/avance.xlsx
+++ b/avance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145B85A6-55A6-4A9E-85CA-5E705DC8E944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE00624-9C5F-4750-8401-B60714389E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="117">
   <si>
     <t>Campo</t>
   </si>
@@ -392,6 +392,12 @@
   </si>
   <si>
     <t>Nuola300</t>
+  </si>
+  <si>
+    <t>Araña</t>
+  </si>
+  <si>
+    <t>Osiris</t>
   </si>
 </sst>
 </file>
@@ -1920,22 +1926,22 @@
         <v>1800</v>
       </c>
       <c r="K15" s="1">
-        <v>30</v>
+        <v>49.78</v>
       </c>
       <c r="L15" s="1">
-        <v>1430</v>
+        <v>1270</v>
       </c>
       <c r="M15" s="9">
         <f t="shared" si="0"/>
-        <v>0.60265166733627962</v>
+        <v>1</v>
       </c>
       <c r="N15" s="10">
         <f t="shared" si="1"/>
-        <v>-370</v>
+        <v>-530</v>
       </c>
       <c r="O15" s="11">
         <f t="shared" si="2"/>
-        <v>-0.20555555555555555</v>
+        <v>-0.29444444444444445</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -1969,17 +1975,23 @@
       <c r="J16" s="1">
         <v>1600</v>
       </c>
+      <c r="K16" s="1">
+        <v>26.67</v>
+      </c>
+      <c r="L16" s="1">
+        <v>800</v>
+      </c>
       <c r="M16" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O16" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="N16" s="10">
+        <f t="shared" si="1"/>
+        <v>-800</v>
+      </c>
+      <c r="O16" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2013,17 +2025,23 @@
       <c r="J17" s="1">
         <v>1600</v>
       </c>
+      <c r="K17" s="1">
+        <v>23</v>
+      </c>
+      <c r="L17" s="1">
+        <v>850</v>
+      </c>
       <c r="M17" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O17" s="11" t="str">
+        <v>0.67726737338044762</v>
+      </c>
+      <c r="N17" s="10">
+        <f t="shared" si="1"/>
+        <v>-750</v>
+      </c>
+      <c r="O17" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-0.46875</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3002,22 +3020,22 @@
         <v>2200</v>
       </c>
       <c r="K37" s="1">
-        <v>270</v>
+        <v>386.2</v>
       </c>
       <c r="L37" s="1">
-        <v>2000</v>
+        <v>2040</v>
       </c>
       <c r="M37" s="9">
         <f t="shared" si="0"/>
-        <v>0.69911962713619891</v>
+        <v>1</v>
       </c>
       <c r="N37" s="10">
         <f t="shared" si="1"/>
-        <v>-200</v>
+        <v>-160</v>
       </c>
       <c r="O37" s="11">
         <f t="shared" si="2"/>
-        <v>-9.0909090909090912E-2</v>
+        <v>-7.2727272727272724E-2</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3383,17 +3401,23 @@
       <c r="J45" s="1">
         <v>1800</v>
       </c>
+      <c r="K45" s="1">
+        <v>30</v>
+      </c>
+      <c r="L45" s="1">
+        <v>2150</v>
+      </c>
       <c r="M45" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N45" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O45" s="11" t="str">
+        <v>0.13324450366422386</v>
+      </c>
+      <c r="N45" s="10">
+        <f t="shared" si="1"/>
+        <v>350</v>
+      </c>
+      <c r="O45" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.19444444444444445</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3470,11 +3494,11 @@
       </c>
       <c r="C50" s="20">
         <f>SUMIF(F$2:F$45,"Sj2",K$2:K$45)</f>
-        <v>3089.69</v>
+        <v>3305.3399999999997</v>
       </c>
       <c r="D50" s="21">
         <f>IF(B50&gt;0,C50/B50,"")</f>
-        <v>0.75801453865648682</v>
+        <v>0.8109214112751868</v>
       </c>
       <c r="E50" s="22">
         <f>IF(SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMIF(F$2:F$45,"Sj2",C$2:C$45),"")</f>
@@ -3482,15 +3506,15 @@
       </c>
       <c r="F50" s="22">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1673.6006524926449</v>
+        <v>1677.4255598516345</v>
       </c>
       <c r="G50" s="23">
         <f>IF(F50&lt;&gt;"",F50-E50,"")</f>
-        <v>-264.29823441446797</v>
+        <v>-260.47332705547842</v>
       </c>
       <c r="H50" s="24">
         <f>IF(AND(F50&lt;&gt;"",E50&gt;0),(F50-E50)/E50,"")</f>
-        <v>-0.13638391362940924</v>
+        <v>-0.13441017424350449</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3503,11 +3527,11 @@
       </c>
       <c r="C51" s="26">
         <f>SUM(C49:C50)</f>
-        <v>3558.36</v>
+        <v>3774.0099999999998</v>
       </c>
       <c r="D51" s="27">
         <f>IF(B51&gt;0,C51/B51,"")</f>
-        <v>0.78296917288269841</v>
+        <v>0.83042004972825467</v>
       </c>
       <c r="E51" s="28">
         <f>IF(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)),"")</f>
@@ -3515,15 +3539,15 @@
       </c>
       <c r="F51" s="28">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1668.5542581413911</v>
+        <v>1672.1925299615</v>
       </c>
       <c r="G51" s="29">
         <f>IF(F51&lt;&gt;"",F51-E51,"")</f>
-        <v>-280.63336700438276</v>
+        <v>-276.99509518427385</v>
       </c>
       <c r="H51" s="30">
         <f>IF(AND(F51&lt;&gt;"",E51&gt;0),(F51-E51)/E51,"")</f>
-        <v>-0.14397452732822222</v>
+        <v>-0.14210796929493036</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3681,11 +3705,11 @@
       </c>
       <c r="D58" s="48">
         <f>SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>199.93</v>
+        <v>269.38</v>
       </c>
       <c r="E58" s="49">
         <f t="shared" si="3"/>
-        <v>0.5377353415814955</v>
+        <v>0.72452931683700927</v>
       </c>
       <c r="F58" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3693,15 +3717,15 @@
       </c>
       <c r="G58" s="50">
         <f>IF(SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Montecristo")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1325.1253438703545</v>
+        <v>1210.7020194520751</v>
       </c>
       <c r="H58" s="51">
         <f t="shared" si="4"/>
-        <v>-427.01290249866133</v>
+        <v>-541.43622691694077</v>
       </c>
       <c r="I58" s="52">
         <f t="shared" si="5"/>
-        <v>-0.24370959505254053</v>
+        <v>-0.30901455866223326</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3861,11 +3885,11 @@
       </c>
       <c r="D63" s="42">
         <f>SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>1023.17</v>
+        <v>1169.3700000000001</v>
       </c>
       <c r="E63" s="43">
         <f t="shared" si="3"/>
-        <v>0.5567696401460529</v>
+        <v>0.63632603975643343</v>
       </c>
       <c r="F63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3873,15 +3897,15 @@
       </c>
       <c r="G63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>2036.4722577870737</v>
+        <v>2048.9710869955616</v>
       </c>
       <c r="H63" s="45">
         <f t="shared" si="4"/>
-        <v>-21.982650276854429</v>
+        <v>-9.4838210683665238</v>
       </c>
       <c r="I63" s="46">
         <f t="shared" si="5"/>
-        <v>-1.0679199330885574E-2</v>
+        <v>-4.607252279957153E-3</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3895,11 +3919,11 @@
       </c>
       <c r="D64" s="55">
         <f>SUM(D55:D63)</f>
-        <v>3558.36</v>
+        <v>3774.01</v>
       </c>
       <c r="E64" s="56">
         <f t="shared" si="3"/>
-        <v>0.78296917288269863</v>
+        <v>0.83042004972825501</v>
       </c>
       <c r="F64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45),"")</f>
@@ -3907,15 +3931,15 @@
       </c>
       <c r="G64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1668.5542581413911</v>
+        <v>1672.1925299615</v>
       </c>
       <c r="H64" s="58">
         <f t="shared" si="4"/>
-        <v>-280.63336700438322</v>
+        <v>-276.99509518427431</v>
       </c>
       <c r="I64" s="59">
         <f t="shared" si="5"/>
-        <v>-0.14397452732822241</v>
+        <v>-0.14210796929493055</v>
       </c>
     </row>
   </sheetData>
@@ -4564,17 +4588,26 @@
       <c r="D22" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="36"/>
+      <c r="E22" s="36">
+        <v>41</v>
+      </c>
       <c r="F22" s="37">
         <f t="shared" si="0"/>
-        <v>40.99</v>
+        <v>-9.9999999999980105E-3</v>
       </c>
       <c r="G22" s="38">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
+        <v>1.000243961941937</v>
+      </c>
+      <c r="H22" s="39">
+        <v>46161</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="23" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
@@ -4590,15 +4623,15 @@
         <v>29</v>
       </c>
       <c r="E23" s="36">
-        <v>50</v>
+        <v>63.11</v>
       </c>
       <c r="F23" s="37">
         <f t="shared" si="0"/>
-        <v>13.11</v>
+        <v>0</v>
       </c>
       <c r="G23" s="38">
         <f t="shared" si="1"/>
-        <v>0.79226746949770244</v>
+        <v>1</v>
       </c>
       <c r="H23" s="39">
         <v>46159</v>
@@ -5352,17 +5385,26 @@
       <c r="D48" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E48" s="36"/>
+      <c r="E48" s="36">
+        <v>52</v>
+      </c>
       <c r="F48" s="37">
         <f t="shared" si="2"/>
-        <v>189.75</v>
+        <v>137.75</v>
       </c>
       <c r="G48" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
+        <v>0.27404479578392621</v>
+      </c>
+      <c r="H48" s="39">
+        <v>46161</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="49" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
@@ -5543,11 +5585,11 @@
       </c>
       <c r="C58" s="15">
         <f>SUMIF(D$2:D$55,"Cz",E$2:E$55)</f>
-        <v>968.24999999999989</v>
+        <v>1022.36</v>
       </c>
       <c r="D58" s="16">
         <f>IF(B58&gt;0,C58/B58,"")</f>
-        <v>0.78986009707549865</v>
+        <v>0.83400089733654204</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5577,11 +5619,11 @@
       </c>
       <c r="C60" s="15">
         <f>SUMIF(D$2:D$55,"Ceb",E$2:E$55)</f>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="D60" s="16">
         <f>IF(B60&gt;0,C60/B60,"")</f>
-        <v>0</v>
+        <v>4.1261981844727985E-2</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5594,11 +5636,11 @@
       </c>
       <c r="C61" s="26">
         <f>SUM(C58:C60)</f>
-        <v>968.24999999999989</v>
+        <v>1074.3600000000001</v>
       </c>
       <c r="D61" s="27">
         <f>IF(B61&gt;0,C61/B61,"")</f>
-        <v>0.31160894163990133</v>
+        <v>0.34575799900877302</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5696,11 +5738,11 @@
       </c>
       <c r="D68" s="20">
         <f>SUMPRODUCT((A$2:A$55="La Campana")*(D$2:D$55="Cz")*E$2:E$55)</f>
-        <v>211.07</v>
+        <v>265.18</v>
       </c>
       <c r="E68" s="21">
         <f t="shared" si="4"/>
-        <v>0.79597993739864981</v>
+        <v>1.000037711656673</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5756,11 +5798,11 @@
       </c>
       <c r="D71" s="15">
         <f>SUMPRODUCT((A$2:A$55="Santa Rafaela")*(D$2:D$55="Ceb")*E$2:E$55)</f>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="E71" s="16">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.1261981844727985E-2</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5774,11 +5816,11 @@
       </c>
       <c r="D72" s="26">
         <f>SUM(D65:D71)</f>
-        <v>968.25</v>
+        <v>1074.3599999999999</v>
       </c>
       <c r="E72" s="27">
         <f t="shared" si="4"/>
-        <v>0.31160894163990138</v>
+        <v>0.34575799900877296</v>
       </c>
     </row>
   </sheetData>

--- a/avance.xlsx
+++ b/avance.xlsx
@@ -8,15 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE00624-9C5F-4750-8401-B60714389E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1727D6E-320C-4D82-AC06-E3FF2D8689FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Avance cosecha" sheetId="1" r:id="rId1"/>
     <sheet name="Avance de siembra" sheetId="2" r:id="rId2"/>
-    <sheet name="Hoja1" sheetId="3" r:id="rId3"/>
-    <sheet name="Hoja2" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Avance cosecha'!$A$1:$O$45</definedName>
@@ -43,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="92">
   <si>
     <t>Campo</t>
   </si>
@@ -298,51 +296,6 @@
     <t>Desvío (%)</t>
   </si>
   <si>
-    <t>SOJA 1ra</t>
-  </si>
-  <si>
-    <t>CAMPO</t>
-  </si>
-  <si>
-    <t>Sup Sembrada</t>
-  </si>
-  <si>
-    <t>Sup Cosechada</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>Sup sin cosechar</t>
-  </si>
-  <si>
-    <t>Tn Secos</t>
-  </si>
-  <si>
-    <t>qq/ha</t>
-  </si>
-  <si>
-    <t>UY_EL MALACARA SOJA 1ra</t>
-  </si>
-  <si>
-    <t>UY_LA CAMPANA SOJA 1ra</t>
-  </si>
-  <si>
-    <t>Total general</t>
-  </si>
-  <si>
-    <t>SOJA 2da</t>
-  </si>
-  <si>
-    <t>UY_EL MALACARA SOJA 2da</t>
-  </si>
-  <si>
-    <t>UY_LA BLANQUEADA SOJA 2da</t>
-  </si>
-  <si>
-    <t>GLOBAL ZONA</t>
-  </si>
-  <si>
     <t>Presicion Planting</t>
   </si>
   <si>
@@ -358,39 +311,6 @@
     <t>Curry/hyola 575</t>
   </si>
   <si>
-    <t>Zona</t>
-  </si>
-  <si>
-    <t>Salto</t>
-  </si>
-  <si>
-    <t>Sembradoras</t>
-  </si>
-  <si>
-    <t>Ancho total (m)</t>
-  </si>
-  <si>
-    <t>Durazno</t>
-  </si>
-  <si>
-    <t>Lit. Norte</t>
-  </si>
-  <si>
-    <t>Siembra</t>
-  </si>
-  <si>
-    <t>Tacuarembó</t>
-  </si>
-  <si>
-    <t>Ruta 20</t>
-  </si>
-  <si>
-    <t>Cosecha</t>
-  </si>
-  <si>
-    <t>Cantidad</t>
-  </si>
-  <si>
     <t>Nuola300</t>
   </si>
   <si>
@@ -398,6 +318,9 @@
   </si>
   <si>
     <t>Osiris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ha Resembradas </t>
   </si>
 </sst>
 </file>
@@ -411,7 +334,7 @@
     <numFmt numFmtId="167" formatCode="\+0.0%;\-0.0%;\-"/>
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,36 +412,14 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Verdana"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -569,30 +470,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF003366"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD8E4BC"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -615,72 +498,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -863,62 +686,28 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3023,7 +2812,7 @@
         <v>386.2</v>
       </c>
       <c r="L37" s="1">
-        <v>2040</v>
+        <v>2044</v>
       </c>
       <c r="M37" s="9">
         <f t="shared" si="0"/>
@@ -3031,11 +2820,11 @@
       </c>
       <c r="N37" s="10">
         <f t="shared" si="1"/>
-        <v>-160</v>
+        <v>-156</v>
       </c>
       <c r="O37" s="11">
         <f t="shared" si="2"/>
-        <v>-7.2727272727272724E-2</v>
+        <v>-7.0909090909090908E-2</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3117,7 +2906,7 @@
         <v>189.75</v>
       </c>
       <c r="L39" s="1">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="M39" s="9">
         <f t="shared" si="0"/>
@@ -3125,11 +2914,11 @@
       </c>
       <c r="N39" s="10">
         <f t="shared" si="1"/>
-        <v>-280</v>
+        <v>-279</v>
       </c>
       <c r="O39" s="11">
         <f t="shared" si="2"/>
-        <v>-0.14000000000000001</v>
+        <v>-0.13950000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3167,7 +2956,7 @@
         <v>169.61</v>
       </c>
       <c r="L40" s="1">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="M40" s="9">
         <f t="shared" si="0"/>
@@ -3175,11 +2964,11 @@
       </c>
       <c r="N40" s="10">
         <f t="shared" si="1"/>
-        <v>-300</v>
+        <v>-303</v>
       </c>
       <c r="O40" s="11">
         <f t="shared" si="2"/>
-        <v>-0.13043478260869565</v>
+        <v>-0.13173913043478261</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3261,7 +3050,7 @@
         <v>243.29</v>
       </c>
       <c r="L42" s="1">
-        <v>2300</v>
+        <v>2295</v>
       </c>
       <c r="M42" s="9">
         <f t="shared" si="0"/>
@@ -3269,11 +3058,11 @@
       </c>
       <c r="N42" s="10">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="O42" s="11">
         <f t="shared" si="2"/>
-        <v>9.5238095238095233E-2</v>
+        <v>9.285714285714286E-2</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3307,17 +3096,23 @@
       <c r="J43" s="1">
         <v>2000</v>
       </c>
+      <c r="K43" s="1">
+        <v>66.290000000000006</v>
+      </c>
+      <c r="L43" s="1">
+        <v>2190</v>
+      </c>
       <c r="M43" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N43" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O43" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>0.32852611755377148</v>
+      </c>
+      <c r="N43" s="10">
+        <f t="shared" si="1"/>
+        <v>190</v>
+      </c>
+      <c r="O43" s="11">
+        <f t="shared" si="2"/>
+        <v>9.5000000000000001E-2</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3402,22 +3197,22 @@
         <v>1800</v>
       </c>
       <c r="K45" s="1">
-        <v>30</v>
+        <v>215</v>
       </c>
       <c r="L45" s="1">
-        <v>2150</v>
+        <v>2130</v>
       </c>
       <c r="M45" s="9">
         <f t="shared" si="0"/>
-        <v>0.13324450366422386</v>
+        <v>0.95491894292693758</v>
       </c>
       <c r="N45" s="10">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="O45" s="11">
         <f t="shared" si="2"/>
-        <v>0.19444444444444445</v>
+        <v>0.18333333333333332</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3494,11 +3289,11 @@
       </c>
       <c r="C50" s="20">
         <f>SUMIF(F$2:F$45,"Sj2",K$2:K$45)</f>
-        <v>3305.3399999999997</v>
+        <v>3556.6299999999997</v>
       </c>
       <c r="D50" s="21">
         <f>IF(B50&gt;0,C50/B50,"")</f>
-        <v>0.8109214112751868</v>
+        <v>0.87257208607394932</v>
       </c>
       <c r="E50" s="22">
         <f>IF(SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMIF(F$2:F$45,"Sj2",C$2:C$45),"")</f>
@@ -3506,15 +3301,15 @@
       </c>
       <c r="F50" s="22">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1677.4255598516345</v>
+        <v>1710.3539502281653</v>
       </c>
       <c r="G50" s="23">
         <f>IF(F50&lt;&gt;"",F50-E50,"")</f>
-        <v>-260.47332705547842</v>
+        <v>-227.54493667894758</v>
       </c>
       <c r="H50" s="24">
         <f>IF(AND(F50&lt;&gt;"",E50&gt;0),(F50-E50)/E50,"")</f>
-        <v>-0.13441017424350449</v>
+        <v>-0.11741837420739187</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3527,11 +3322,11 @@
       </c>
       <c r="C51" s="26">
         <f>SUM(C49:C50)</f>
-        <v>3774.0099999999998</v>
+        <v>4025.2999999999997</v>
       </c>
       <c r="D51" s="27">
         <f>IF(B51&gt;0,C51/B51,"")</f>
-        <v>0.83042004972825467</v>
+        <v>0.88571302836270804</v>
       </c>
       <c r="E51" s="28">
         <f>IF(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)),"")</f>
@@ -3539,15 +3334,15 @@
       </c>
       <c r="F51" s="28">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1672.1925299615</v>
+        <v>1701.6137182321813</v>
       </c>
       <c r="G51" s="29">
         <f>IF(F51&lt;&gt;"",F51-E51,"")</f>
-        <v>-276.99509518427385</v>
+        <v>-247.57390691359251</v>
       </c>
       <c r="H51" s="30">
         <f>IF(AND(F51&lt;&gt;"",E51&gt;0),(F51-E51)/E51,"")</f>
-        <v>-0.14210796929493036</v>
+        <v>-0.12701389220808193</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3885,11 +3680,11 @@
       </c>
       <c r="D63" s="42">
         <f>SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>1169.3700000000001</v>
+        <v>1420.66</v>
       </c>
       <c r="E63" s="43">
         <f t="shared" si="3"/>
-        <v>0.63632603975643343</v>
+        <v>0.77306836299920012</v>
       </c>
       <c r="F63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3897,15 +3692,15 @@
       </c>
       <c r="G63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>2048.9710869955616</v>
+        <v>2065.6875607112183</v>
       </c>
       <c r="H63" s="45">
         <f t="shared" si="4"/>
-        <v>-9.4838210683665238</v>
+        <v>7.2326526472902515</v>
       </c>
       <c r="I63" s="46">
         <f t="shared" si="5"/>
-        <v>-4.607252279957153E-3</v>
+        <v>3.5136318113924074E-3</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3919,11 +3714,11 @@
       </c>
       <c r="D64" s="55">
         <f>SUM(D55:D63)</f>
-        <v>3774.01</v>
+        <v>4025.3</v>
       </c>
       <c r="E64" s="56">
         <f t="shared" si="3"/>
-        <v>0.83042004972825501</v>
+        <v>0.88571302836270827</v>
       </c>
       <c r="F64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45),"")</f>
@@ -3931,15 +3726,15 @@
       </c>
       <c r="G64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1672.1925299615</v>
+        <v>1701.6137182321813</v>
       </c>
       <c r="H64" s="58">
         <f t="shared" si="4"/>
-        <v>-276.99509518427431</v>
+        <v>-247.57390691359296</v>
       </c>
       <c r="I64" s="59">
         <f t="shared" si="5"/>
-        <v>-0.14210796929493055</v>
+        <v>-0.12701389220808212</v>
       </c>
     </row>
   </sheetData>
@@ -3958,7 +3753,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
@@ -3971,10 +3766,13 @@
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
     <col min="9" max="9" width="25.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="1"/>
+    <col min="11" max="11" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11.42578125" style="1"/>
+    <col min="14" max="14" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4002,11 +3800,26 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J1" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -4031,7 +3844,7 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
     </row>
-    <row r="3" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
@@ -4062,7 +3875,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -4093,7 +3906,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -4124,7 +3937,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
@@ -4155,7 +3968,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
@@ -4186,7 +3999,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
@@ -4217,7 +4030,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>15</v>
       </c>
@@ -4248,7 +4061,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>15</v>
       </c>
@@ -4279,7 +4092,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
@@ -4310,7 +4123,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>27</v>
       </c>
@@ -4341,7 +4154,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>27</v>
       </c>
@@ -4366,7 +4179,7 @@
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>27</v>
       </c>
@@ -4391,7 +4204,7 @@
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>27</v>
       </c>
@@ -4416,7 +4229,7 @@
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
     </row>
-    <row r="16" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>27</v>
       </c>
@@ -4441,7 +4254,7 @@
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
     </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>27</v>
       </c>
@@ -4466,7 +4279,7 @@
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
     </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>27</v>
       </c>
@@ -4491,7 +4304,7 @@
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
     </row>
-    <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
@@ -4516,7 +4329,7 @@
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
     </row>
-    <row r="20" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>30</v>
       </c>
@@ -4541,7 +4354,7 @@
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
     </row>
-    <row r="21" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>33</v>
       </c>
@@ -4569,13 +4382,13 @@
         <v>46160</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>33</v>
       </c>
@@ -4603,13 +4416,13 @@
         <v>46161</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
@@ -4637,13 +4450,13 @@
         <v>46159</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>33</v>
       </c>
@@ -4671,13 +4484,13 @@
         <v>46157</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>33</v>
       </c>
@@ -4708,7 +4521,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>33</v>
       </c>
@@ -4739,7 +4552,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>33</v>
       </c>
@@ -4767,13 +4580,13 @@
         <v>46158</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>33</v>
       </c>
@@ -4804,7 +4617,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>35</v>
       </c>
@@ -4832,13 +4645,29 @@
         <v>46143</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+      <c r="K29" s="1">
+        <v>40</v>
+      </c>
+      <c r="L29" s="67">
+        <f>+K29/C29</f>
+        <v>0.28801843317972353</v>
+      </c>
+      <c r="M29" s="62">
+        <v>46162</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>35</v>
       </c>
@@ -4869,7 +4698,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>36</v>
       </c>
@@ -4894,7 +4723,7 @@
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
     </row>
-    <row r="32" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>36</v>
       </c>
@@ -4925,7 +4754,7 @@
         <v>68</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -4959,7 +4788,7 @@
         <v>68</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -4993,7 +4822,7 @@
         <v>68</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
@@ -5145,7 +4974,7 @@
         <v>68</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
@@ -5386,24 +5215,24 @@
         <v>38</v>
       </c>
       <c r="E48" s="36">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="F48" s="37">
         <f t="shared" si="2"/>
-        <v>137.75</v>
+        <v>69.75</v>
       </c>
       <c r="G48" s="38">
         <f t="shared" si="3"/>
-        <v>0.27404479578392621</v>
+        <v>0.6324110671936759</v>
       </c>
       <c r="H48" s="39">
         <v>46161</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -5619,11 +5448,11 @@
       </c>
       <c r="C60" s="15">
         <f>SUMIF(D$2:D$55,"Ceb",E$2:E$55)</f>
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="D60" s="16">
         <f>IF(B60&gt;0,C60/B60,"")</f>
-        <v>4.1261981844727985E-2</v>
+        <v>9.5219958103218427E-2</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5636,11 +5465,11 @@
       </c>
       <c r="C61" s="26">
         <f>SUM(C58:C60)</f>
-        <v>1074.3600000000001</v>
+        <v>1142.3600000000001</v>
       </c>
       <c r="D61" s="27">
         <f>IF(B61&gt;0,C61/B61,"")</f>
-        <v>0.34575799900877302</v>
+        <v>0.36764223141932123</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5746,21 +5575,21 @@
       </c>
     </row>
     <row r="69" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="76" t="s">
+      <c r="A69" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="B69" s="77" t="s">
+      <c r="B69" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="C69" s="78">
+      <c r="C69" s="65">
         <f>SUMPRODUCT((A$2:A$55="San Luis")*(D$2:D$55="Cz")*C$2:C$55)</f>
         <v>138.88</v>
       </c>
-      <c r="D69" s="78">
+      <c r="D69" s="65">
         <f>SUMPRODUCT((A$2:A$55="San Luis")*(D$2:D$55="Cz")*E$2:E$55)</f>
         <v>138.88</v>
       </c>
-      <c r="E69" s="79">
+      <c r="E69" s="66">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -5798,11 +5627,11 @@
       </c>
       <c r="D71" s="15">
         <f>SUMPRODUCT((A$2:A$55="Santa Rafaela")*(D$2:D$55="Ceb")*E$2:E$55)</f>
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="E71" s="16">
         <f t="shared" si="4"/>
-        <v>4.1261981844727985E-2</v>
+        <v>9.5219958103218427E-2</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5816,11 +5645,11 @@
       </c>
       <c r="D72" s="26">
         <f>SUM(D65:D71)</f>
-        <v>1074.3599999999999</v>
+        <v>1142.3599999999999</v>
       </c>
       <c r="E72" s="27">
         <f t="shared" si="4"/>
-        <v>0.34575799900877296</v>
+        <v>0.36764223141932112</v>
       </c>
     </row>
   </sheetData>
@@ -5836,489 +5665,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF28F8F1-453C-4259-97F7-9810D6B71FDA}">
-  <dimension ref="B1:L14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B1" s="62" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-    </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="64" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="65" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="65" t="s">
-        <v>87</v>
-      </c>
-      <c r="F2" s="65" t="s">
-        <v>88</v>
-      </c>
-      <c r="G2" s="65" t="s">
-        <v>89</v>
-      </c>
-      <c r="H2" s="65" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="69" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="66">
-        <v>203</v>
-      </c>
-      <c r="D3" s="66">
-        <v>203</v>
-      </c>
-      <c r="E3" s="67">
-        <v>1</v>
-      </c>
-      <c r="F3" s="66">
-        <v>0</v>
-      </c>
-      <c r="G3" s="66">
-        <v>444</v>
-      </c>
-      <c r="H3" s="68">
-        <v>21.8</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="66">
-        <v>265</v>
-      </c>
-      <c r="D4" s="66">
-        <v>220</v>
-      </c>
-      <c r="E4" s="67">
-        <v>0.83</v>
-      </c>
-      <c r="F4" s="66">
-        <v>45</v>
-      </c>
-      <c r="G4" s="66">
-        <v>276</v>
-      </c>
-      <c r="H4" s="68">
-        <v>12.6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="64" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="65">
-        <v>469</v>
-      </c>
-      <c r="D5" s="65">
-        <v>423</v>
-      </c>
-      <c r="E5" s="70">
-        <v>0.9</v>
-      </c>
-      <c r="F5" s="65">
-        <v>45</v>
-      </c>
-      <c r="G5" s="65">
-        <v>720</v>
-      </c>
-      <c r="H5" s="65">
-        <v>17</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="L5" s="73">
-        <v>46149</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="K6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="1">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="K7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7" s="1">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="64" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" s="65" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" s="65" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" s="65" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" s="65" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" s="65" t="s">
-        <v>89</v>
-      </c>
-      <c r="H8" s="65" t="s">
-        <v>90</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="69" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="66">
-        <v>769</v>
-      </c>
-      <c r="D9" s="66">
-        <v>261</v>
-      </c>
-      <c r="E9" s="67">
-        <v>0.34</v>
-      </c>
-      <c r="F9" s="66">
-        <v>508</v>
-      </c>
-      <c r="G9" s="66">
-        <v>421</v>
-      </c>
-      <c r="H9" s="68">
-        <v>16.2</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L9" s="1">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="69" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="66">
-        <v>494</v>
-      </c>
-      <c r="D10" s="66">
-        <v>407</v>
-      </c>
-      <c r="E10" s="67">
-        <v>0.82</v>
-      </c>
-      <c r="F10" s="66">
-        <v>87</v>
-      </c>
-      <c r="G10" s="66">
-        <v>595</v>
-      </c>
-      <c r="H10" s="68">
-        <v>14.6</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="1">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="64" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="71">
-        <v>4388</v>
-      </c>
-      <c r="D11" s="65">
-        <v>668</v>
-      </c>
-      <c r="E11" s="70">
-        <v>0.15</v>
-      </c>
-      <c r="F11" s="71">
-        <v>3720</v>
-      </c>
-      <c r="G11" s="71">
-        <v>1016</v>
-      </c>
-      <c r="H11" s="65">
-        <v>15.2</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="63"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" s="65" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" s="65" t="s">
-        <v>86</v>
-      </c>
-      <c r="E13" s="65" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" s="65" t="s">
-        <v>88</v>
-      </c>
-      <c r="G13" s="65" t="s">
-        <v>89</v>
-      </c>
-      <c r="H13" s="72" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="64"/>
-      <c r="C14" s="71">
-        <v>4857</v>
-      </c>
-      <c r="D14" s="71">
-        <v>1092</v>
-      </c>
-      <c r="E14" s="70">
-        <v>0.22</v>
-      </c>
-      <c r="F14" s="71">
-        <v>3765</v>
-      </c>
-      <c r="G14" s="71">
-        <v>1736</v>
-      </c>
-      <c r="H14" s="72">
-        <v>15.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{504CE239-D04F-47C2-AFE1-1D260465006A}">
-  <dimension ref="B1:F9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D1" s="80" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" s="80"/>
-      <c r="F1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3">
-        <v>900</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="74">
-        <f>60*0.38</f>
-        <v>22.8</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4">
-        <v>3000</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4" s="74">
-        <f>122*0.38</f>
-        <v>46.36</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5">
-        <v>5700</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>83</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C6">
-        <v>4300</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <f>+D6*13</f>
-        <v>78</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7">
-        <v>8600</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <f>+D7*13</f>
-        <v>65</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C8">
-        <f>SUM(C3:C7)</f>
-        <v>22500</v>
-      </c>
-      <c r="D8">
-        <f>SUM(D3:D7)</f>
-        <v>23</v>
-      </c>
-      <c r="E8" s="74">
-        <f>SUM(E3:E7)</f>
-        <v>295.15999999999997</v>
-      </c>
-      <c r="F8">
-        <f>SUM(F3:F7)</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E9" s="75">
-        <f>+C8/E8</f>
-        <v>76.229841441929807</v>
-      </c>
-      <c r="F9" s="75">
-        <f>+C8/F8</f>
-        <v>1022.7272727272727</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/avance.xlsx
+++ b/avance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1727D6E-320C-4D82-AC06-E3FF2D8689FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BA58D1-75B4-4114-893A-ED243ADE5CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="93">
   <si>
     <t>Campo</t>
   </si>
@@ -321,6 +321,9 @@
   </si>
   <si>
     <t xml:space="preserve">ha Resembradas </t>
+  </si>
+  <si>
+    <t>Olimpia</t>
   </si>
 </sst>
 </file>
@@ -2858,17 +2861,23 @@
       <c r="J38" s="1">
         <v>2000</v>
       </c>
+      <c r="K38" s="1">
+        <v>145</v>
+      </c>
+      <c r="L38" s="1">
+        <v>2250</v>
+      </c>
       <c r="M38" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N38" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O38" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>0.94746471510716157</v>
+      </c>
+      <c r="N38" s="10">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="O38" s="11">
+        <f t="shared" si="2"/>
+        <v>0.125</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3097,22 +3106,22 @@
         <v>2000</v>
       </c>
       <c r="K43" s="1">
-        <v>66.290000000000006</v>
+        <v>144</v>
       </c>
       <c r="L43" s="1">
-        <v>2190</v>
+        <v>2050</v>
       </c>
       <c r="M43" s="9">
         <f t="shared" si="0"/>
-        <v>0.32852611755377148</v>
+        <v>0.71364852809991075</v>
       </c>
       <c r="N43" s="10">
         <f t="shared" si="1"/>
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="O43" s="11">
         <f t="shared" si="2"/>
-        <v>9.5000000000000001E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3197,22 +3206,22 @@
         <v>1800</v>
       </c>
       <c r="K45" s="1">
-        <v>215</v>
+        <v>225.15</v>
       </c>
       <c r="L45" s="1">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="M45" s="9">
         <f t="shared" si="0"/>
-        <v>0.95491894292693758</v>
+        <v>1</v>
       </c>
       <c r="N45" s="10">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="O45" s="11">
         <f t="shared" si="2"/>
-        <v>0.18333333333333332</v>
+        <v>0.17777777777777778</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3289,11 +3298,11 @@
       </c>
       <c r="C50" s="20">
         <f>SUMIF(F$2:F$45,"Sj2",K$2:K$45)</f>
-        <v>3556.6299999999997</v>
+        <v>3789.49</v>
       </c>
       <c r="D50" s="21">
         <f>IF(B50&gt;0,C50/B50,"")</f>
-        <v>0.87257208607394932</v>
+        <v>0.92970120435816217</v>
       </c>
       <c r="E50" s="22">
         <f>IF(SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMIF(F$2:F$45,"Sj2",C$2:C$45),"")</f>
@@ -3301,15 +3310,15 @@
       </c>
       <c r="F50" s="22">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1710.3539502281653</v>
+        <v>1736.0486688182314</v>
       </c>
       <c r="G50" s="23">
         <f>IF(F50&lt;&gt;"",F50-E50,"")</f>
-        <v>-227.54493667894758</v>
+        <v>-201.85021808888155</v>
       </c>
       <c r="H50" s="24">
         <f>IF(AND(F50&lt;&gt;"",E50&gt;0),(F50-E50)/E50,"")</f>
-        <v>-0.11741837420739187</v>
+        <v>-0.10415931370445985</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3322,11 +3331,11 @@
       </c>
       <c r="C51" s="26">
         <f>SUM(C49:C50)</f>
-        <v>4025.2999999999997</v>
+        <v>4258.16</v>
       </c>
       <c r="D51" s="27">
         <f>IF(B51&gt;0,C51/B51,"")</f>
-        <v>0.88571302836270804</v>
+        <v>0.93695073382181426</v>
       </c>
       <c r="E51" s="28">
         <f>IF(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)),"")</f>
@@ -3334,15 +3343,15 @@
       </c>
       <c r="F51" s="28">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1701.6137182321813</v>
+        <v>1724.9583388130084</v>
       </c>
       <c r="G51" s="29">
         <f>IF(F51&lt;&gt;"",F51-E51,"")</f>
-        <v>-247.57390691359251</v>
+        <v>-224.22928633276547</v>
       </c>
       <c r="H51" s="30">
         <f>IF(AND(F51&lt;&gt;"",E51&gt;0),(F51-E51)/E51,"")</f>
-        <v>-0.12701389220808193</v>
+        <v>-0.11503730243310777</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3680,11 +3689,11 @@
       </c>
       <c r="D63" s="42">
         <f>SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>1420.66</v>
+        <v>1653.5200000000002</v>
       </c>
       <c r="E63" s="43">
         <f t="shared" si="3"/>
-        <v>0.77306836299920012</v>
+        <v>0.89978179127056257</v>
       </c>
       <c r="F63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3692,15 +3701,15 @@
       </c>
       <c r="G63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>2065.6875607112183</v>
+        <v>2074.5334740432527</v>
       </c>
       <c r="H63" s="45">
         <f t="shared" si="4"/>
-        <v>7.2326526472902515</v>
+        <v>16.078565979324594</v>
       </c>
       <c r="I63" s="46">
         <f t="shared" si="5"/>
-        <v>3.5136318113924074E-3</v>
+        <v>7.8109877055539817E-3</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3714,11 +3723,11 @@
       </c>
       <c r="D64" s="55">
         <f>SUM(D55:D63)</f>
-        <v>4025.3</v>
+        <v>4258.1600000000008</v>
       </c>
       <c r="E64" s="56">
         <f t="shared" si="3"/>
-        <v>0.88571302836270827</v>
+        <v>0.9369507338218146</v>
       </c>
       <c r="F64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45),"")</f>
@@ -3726,15 +3735,15 @@
       </c>
       <c r="G64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1701.6137182321813</v>
+        <v>1724.9583388130084</v>
       </c>
       <c r="H64" s="58">
         <f t="shared" si="4"/>
-        <v>-247.57390691359296</v>
+        <v>-224.22928633276592</v>
       </c>
       <c r="I64" s="59">
         <f t="shared" si="5"/>
-        <v>-0.12701389220808212</v>
+        <v>-0.11503730243310797</v>
       </c>
     </row>
   </sheetData>
@@ -4651,11 +4660,11 @@
         <v>86</v>
       </c>
       <c r="K29" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L29" s="67">
         <f>+K29/C29</f>
-        <v>0.28801843317972353</v>
+        <v>0.57603686635944706</v>
       </c>
       <c r="M29" s="62">
         <v>46162</v>
@@ -5215,15 +5224,15 @@
         <v>38</v>
       </c>
       <c r="E48" s="36">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="F48" s="37">
         <f t="shared" si="2"/>
-        <v>69.75</v>
+        <v>24.75</v>
       </c>
       <c r="G48" s="38">
         <f t="shared" si="3"/>
-        <v>0.6324110671936759</v>
+        <v>0.86956521739130432</v>
       </c>
       <c r="H48" s="39">
         <v>46161</v>
@@ -5235,7 +5244,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>39</v>
       </c>
@@ -5260,7 +5269,7 @@
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
     </row>
-    <row r="50" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>39</v>
       </c>
@@ -5285,7 +5294,7 @@
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
     </row>
-    <row r="51" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>39</v>
       </c>
@@ -5298,19 +5307,28 @@
       <c r="D51" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E51" s="36"/>
+      <c r="E51" s="36">
+        <v>20</v>
+      </c>
       <c r="F51" s="37">
         <f t="shared" si="2"/>
-        <v>243.29</v>
+        <v>223.29</v>
       </c>
       <c r="G51" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-    </row>
-    <row r="52" spans="1:9" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>8.2206420321427109E-2</v>
+      </c>
+      <c r="H51" s="39">
+        <v>46163</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>39</v>
       </c>
@@ -5335,7 +5353,7 @@
       <c r="H52" s="8"/>
       <c r="I52" s="8"/>
     </row>
-    <row r="53" spans="1:9" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>39</v>
       </c>
@@ -5360,7 +5378,7 @@
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
     </row>
-    <row r="54" spans="1:9" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>39</v>
       </c>
@@ -5385,12 +5403,12 @@
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
     </row>
-    <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>52</v>
       </c>
@@ -5404,7 +5422,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="31" t="s">
         <v>75</v>
       </c>
@@ -5421,7 +5439,7 @@
         <v>0.83400089733654204</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="33" t="s">
         <v>76</v>
       </c>
@@ -5438,7 +5456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="31" t="s">
         <v>77</v>
       </c>
@@ -5448,14 +5466,14 @@
       </c>
       <c r="C60" s="15">
         <f>SUMIF(D$2:D$55,"Ceb",E$2:E$55)</f>
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="D60" s="16">
         <f>IF(B60&gt;0,C60/B60,"")</f>
-        <v>9.5219958103218427E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.14679743540912843</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="25" t="s">
         <v>60</v>
       </c>
@@ -5465,19 +5483,19 @@
       </c>
       <c r="C61" s="26">
         <f>SUM(C58:C60)</f>
-        <v>1142.3600000000001</v>
+        <v>1207.3600000000001</v>
       </c>
       <c r="D61" s="27">
         <f>IF(B61&gt;0,C61/B61,"")</f>
-        <v>0.36764223141932123</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.38856098298822761</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
         <v>0</v>
       </c>
@@ -5627,11 +5645,11 @@
       </c>
       <c r="D71" s="15">
         <f>SUMPRODUCT((A$2:A$55="Santa Rafaela")*(D$2:D$55="Ceb")*E$2:E$55)</f>
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="E71" s="16">
         <f t="shared" si="4"/>
-        <v>9.5219958103218427E-2</v>
+        <v>0.14679743540912843</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5645,11 +5663,11 @@
       </c>
       <c r="D72" s="26">
         <f>SUM(D65:D71)</f>
-        <v>1142.3599999999999</v>
+        <v>1207.3599999999999</v>
       </c>
       <c r="E72" s="27">
         <f t="shared" si="4"/>
-        <v>0.36764223141932112</v>
+        <v>0.3885609829882275</v>
       </c>
     </row>
   </sheetData>

--- a/avance.xlsx
+++ b/avance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BA58D1-75B4-4114-893A-ED243ADE5CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5B2868-2B0D-4B52-AEBE-924264D97B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Avance cosecha" sheetId="1" r:id="rId1"/>
@@ -2815,7 +2815,7 @@
         <v>386.2</v>
       </c>
       <c r="L37" s="1">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="M37" s="9">
         <f t="shared" si="0"/>
@@ -2823,11 +2823,11 @@
       </c>
       <c r="N37" s="10">
         <f t="shared" si="1"/>
-        <v>-156</v>
+        <v>-155</v>
       </c>
       <c r="O37" s="11">
         <f t="shared" si="2"/>
-        <v>-7.0909090909090908E-2</v>
+        <v>-7.045454545454545E-2</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2862,22 +2862,22 @@
         <v>2000</v>
       </c>
       <c r="K38" s="1">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="L38" s="1">
-        <v>2250</v>
+        <v>2130</v>
       </c>
       <c r="M38" s="9">
         <f t="shared" si="0"/>
-        <v>0.94746471510716157</v>
+        <v>0.99973863042341882</v>
       </c>
       <c r="N38" s="10">
         <f t="shared" si="1"/>
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="O38" s="11">
         <f t="shared" si="2"/>
-        <v>0.125</v>
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -2915,7 +2915,7 @@
         <v>189.75</v>
       </c>
       <c r="L39" s="1">
-        <v>1721</v>
+        <v>2042</v>
       </c>
       <c r="M39" s="9">
         <f t="shared" si="0"/>
@@ -2923,11 +2923,11 @@
       </c>
       <c r="N39" s="10">
         <f t="shared" si="1"/>
-        <v>-279</v>
+        <v>42</v>
       </c>
       <c r="O39" s="11">
         <f t="shared" si="2"/>
-        <v>-0.13950000000000001</v>
+        <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3011,17 +3011,23 @@
       <c r="J41" s="1">
         <v>2000</v>
       </c>
+      <c r="K41" s="1">
+        <v>118.35</v>
+      </c>
+      <c r="L41" s="1">
+        <v>2488</v>
+      </c>
       <c r="M41" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N41" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O41" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="N41" s="10">
+        <f t="shared" si="1"/>
+        <v>488</v>
+      </c>
+      <c r="O41" s="11">
+        <f t="shared" si="2"/>
+        <v>0.24399999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3106,22 +3112,22 @@
         <v>2000</v>
       </c>
       <c r="K43" s="1">
-        <v>144</v>
+        <v>201.78</v>
       </c>
       <c r="L43" s="1">
-        <v>2050</v>
+        <v>2329</v>
       </c>
       <c r="M43" s="9">
         <f t="shared" si="0"/>
-        <v>0.71364852809991075</v>
+        <v>1</v>
       </c>
       <c r="N43" s="10">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>329</v>
       </c>
       <c r="O43" s="11">
         <f t="shared" si="2"/>
-        <v>2.5000000000000001E-2</v>
+        <v>0.16450000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -3209,7 +3215,7 @@
         <v>225.15</v>
       </c>
       <c r="L45" s="1">
-        <v>2120</v>
+        <v>2052</v>
       </c>
       <c r="M45" s="9">
         <f t="shared" si="0"/>
@@ -3217,11 +3223,11 @@
       </c>
       <c r="N45" s="10">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>252</v>
       </c>
       <c r="O45" s="11">
         <f t="shared" si="2"/>
-        <v>0.17777777777777778</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3298,11 +3304,11 @@
       </c>
       <c r="C50" s="20">
         <f>SUMIF(F$2:F$45,"Sj2",K$2:K$45)</f>
-        <v>3789.49</v>
+        <v>3973.62</v>
       </c>
       <c r="D50" s="21">
         <f>IF(B50&gt;0,C50/B50,"")</f>
-        <v>0.92970120435816217</v>
+        <v>0.97487506225420317</v>
       </c>
       <c r="E50" s="22">
         <f>IF(SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMIF(F$2:F$45,"Sj2",C$2:C$45),"")</f>
@@ -3310,15 +3316,15 @@
       </c>
       <c r="F50" s="22">
         <f>IF(SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1736.0486688182314</v>
+        <v>1785.1644696775234</v>
       </c>
       <c r="G50" s="23">
         <f>IF(F50&lt;&gt;"",F50-E50,"")</f>
-        <v>-201.85021808888155</v>
+        <v>-152.73441722958955</v>
       </c>
       <c r="H50" s="24">
         <f>IF(AND(F50&lt;&gt;"",E50&gt;0),(F50-E50)/E50,"")</f>
-        <v>-0.10415931370445985</v>
+        <v>-7.8814440867631494E-2</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3331,11 +3337,11 @@
       </c>
       <c r="C51" s="26">
         <f>SUM(C49:C50)</f>
-        <v>4258.16</v>
+        <v>4442.29</v>
       </c>
       <c r="D51" s="27">
         <f>IF(B51&gt;0,C51/B51,"")</f>
-        <v>0.93695073382181426</v>
+        <v>0.97746605936585462</v>
       </c>
       <c r="E51" s="28">
         <f>IF(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/(SUMIF(F$2:F$45,"Sj1",C$2:C$45)+SUMIF(F$2:F$45,"Sj2",C$2:C$45)),"")</f>
@@ -3343,15 +3349,15 @@
       </c>
       <c r="F51" s="28">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1724.9583388130084</v>
+        <v>1769.3520166400663</v>
       </c>
       <c r="G51" s="29">
         <f>IF(F51&lt;&gt;"",F51-E51,"")</f>
-        <v>-224.22928633276547</v>
+        <v>-179.83560850570757</v>
       </c>
       <c r="H51" s="30">
         <f>IF(AND(F51&lt;&gt;"",E51&gt;0),(F51-E51)/E51,"")</f>
-        <v>-0.11503730243310777</v>
+        <v>-9.2261825483454019E-2</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3689,11 +3695,11 @@
       </c>
       <c r="D63" s="42">
         <f>SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*K$2:K$45)</f>
-        <v>1653.5200000000002</v>
+        <v>1837.65</v>
       </c>
       <c r="E63" s="43">
         <f t="shared" si="3"/>
-        <v>0.89978179127056257</v>
+        <v>0.99997823354319826</v>
       </c>
       <c r="F63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45*J$2:J$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*C$2:C$45),"")</f>
@@ -3701,15 +3707,15 @@
       </c>
       <c r="G63" s="44">
         <f>IF(SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT((A$2:A$45="Santa Rafaela")*(F$2:F$45="Sj2")*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>2074.5334740432527</v>
+        <v>2146.8227137920708</v>
       </c>
       <c r="H63" s="45">
         <f t="shared" si="4"/>
-        <v>16.078565979324594</v>
+        <v>88.367805728142685</v>
       </c>
       <c r="I63" s="46">
         <f t="shared" si="5"/>
-        <v>7.8109877055539817E-3</v>
+        <v>4.2929191881719037E-2</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3723,11 +3729,11 @@
       </c>
       <c r="D64" s="55">
         <f>SUM(D55:D63)</f>
-        <v>4258.1600000000008</v>
+        <v>4442.2900000000009</v>
       </c>
       <c r="E64" s="56">
         <f t="shared" si="3"/>
-        <v>0.9369507338218146</v>
+        <v>0.97746605936585496</v>
       </c>
       <c r="F64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45*J$2:J$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*C$2:C$45),"")</f>
@@ -3735,15 +3741,15 @@
       </c>
       <c r="G64" s="57">
         <f>IF(SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45)&gt;0,SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45*L$2:L$45)/SUMPRODUCT(((F$2:F$45="Sj1")+(F$2:F$45="Sj2"))*(K$2:K$45&gt;0)*K$2:K$45),"")</f>
-        <v>1724.9583388130084</v>
+        <v>1769.3520166400663</v>
       </c>
       <c r="H64" s="58">
         <f t="shared" si="4"/>
-        <v>-224.22928633276592</v>
+        <v>-179.83560850570802</v>
       </c>
       <c r="I64" s="59">
         <f t="shared" si="5"/>
-        <v>-0.11503730243310797</v>
+        <v>-9.2261825483454227E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4660,11 +4666,11 @@
         <v>86</v>
       </c>
       <c r="K29" s="1">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="L29" s="67">
         <f>+K29/C29</f>
-        <v>0.57603686635944706</v>
+        <v>1.0008640552995391</v>
       </c>
       <c r="M29" s="62">
         <v>46162</v>
@@ -5224,15 +5230,15 @@
         <v>38</v>
       </c>
       <c r="E48" s="36">
-        <v>165</v>
+        <v>189.75</v>
       </c>
       <c r="F48" s="37">
         <f t="shared" si="2"/>
-        <v>24.75</v>
+        <v>0</v>
       </c>
       <c r="G48" s="38">
         <f t="shared" si="3"/>
-        <v>0.86956521739130432</v>
+        <v>1</v>
       </c>
       <c r="H48" s="39">
         <v>46161</v>
@@ -5308,15 +5314,15 @@
         <v>38</v>
       </c>
       <c r="E51" s="36">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F51" s="37">
         <f t="shared" si="2"/>
-        <v>223.29</v>
+        <v>143.29</v>
       </c>
       <c r="G51" s="38">
         <f t="shared" si="3"/>
-        <v>8.2206420321427109E-2</v>
+        <v>0.41103210160713555</v>
       </c>
       <c r="H51" s="39">
         <v>46163</v>
@@ -5466,11 +5472,11 @@
       </c>
       <c r="C60" s="15">
         <f>SUMIF(D$2:D$55,"Ceb",E$2:E$55)</f>
-        <v>185</v>
+        <v>289.75</v>
       </c>
       <c r="D60" s="16">
         <f>IF(B60&gt;0,C60/B60,"")</f>
-        <v>0.14679743540912843</v>
+        <v>0.2299165238367295</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5483,11 +5489,11 @@
       </c>
       <c r="C61" s="26">
         <f>SUM(C58:C60)</f>
-        <v>1207.3600000000001</v>
+        <v>1312.1100000000001</v>
       </c>
       <c r="D61" s="27">
         <f>IF(B61&gt;0,C61/B61,"")</f>
-        <v>0.38856098298822761</v>
+        <v>0.42227235570888821</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5645,11 +5651,11 @@
       </c>
       <c r="D71" s="15">
         <f>SUMPRODUCT((A$2:A$55="Santa Rafaela")*(D$2:D$55="Ceb")*E$2:E$55)</f>
-        <v>185</v>
+        <v>289.75</v>
       </c>
       <c r="E71" s="16">
         <f t="shared" si="4"/>
-        <v>0.14679743540912843</v>
+        <v>0.2299165238367295</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5663,11 +5669,11 @@
       </c>
       <c r="D72" s="26">
         <f>SUM(D65:D71)</f>
-        <v>1207.3599999999999</v>
+        <v>1312.11</v>
       </c>
       <c r="E72" s="27">
         <f t="shared" si="4"/>
-        <v>0.3885609829882275</v>
+        <v>0.42227235570888816</v>
       </c>
     </row>
   </sheetData>
